--- a/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
+++ b/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-12" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,8 +82,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.39</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>26875000</v>
+        <v>108738600</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.64</v>
+        <v>0.25</v>
       </c>
       <c r="H2" t="n">
-        <v>70.36</v>
+        <v>23.54</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.358</v>
+        <v>0.166</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.236</v>
+        <v>0.386</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0.0588</v>
+        <v>0.345</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>8077500</v>
+        <v>46802700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.02</v>
+        <v>0.77</v>
       </c>
       <c r="H3" t="n">
-        <v>25.03</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.38</v>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.167</v>
+        <v>0.285</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.386</v>
+        <v>0.247</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LUSTER</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1.59</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>-0.1543</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6775500</v>
+        <v>16439700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.25</v>
+        <v>4.25</v>
       </c>
       <c r="H4" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+        <v>24.01</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.026</v>
+        <v>1.87</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.028</v>
+        <v>2.015</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.1064</v>
+        <v>0.0095</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2778600</v>
+        <v>12813100</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H5" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.25</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.878</v>
+        <v>1.85</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.017</v>
+        <v>1.658</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,36 +723,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>-0.0426</v>
+        <v>0.515</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1590800</v>
+        <v>11024500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
-        <v>30.66</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+        <v>60.66</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.48</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
     </row>
@@ -764,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-0.008</v>
+        <v>0.18</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1541200</v>
+        <v>10790600</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H7" t="n">
-        <v>68.95999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.586</v>
+        <v>0.168</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.51</v>
+        <v>0.133</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -809,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.0476</v>
+        <v>2.87</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1307000</v>
+        <v>9451700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>4.77</v>
+        <v>0.53</v>
       </c>
       <c r="H8" t="n">
-        <v>68.95999999999999</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.296</v>
+        <v>2.649</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.297</v>
+        <v>2.511</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -854,40 +858,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.0145</v>
+        <v>0.25</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1114200</v>
+        <v>9311200</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H9" t="n">
-        <v>79.16</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.247</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
@@ -899,39 +896,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>LUSTER</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0.0237</v>
+        <v>0.025</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1078800</v>
+        <v>6775500</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.04</v>
+        <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>77.27</v>
+        <v>41.7</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.853</v>
+        <v>0.026</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.659</v>
+        <v>0.028</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -944,39 +941,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.0238</v>
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>934100</v>
+        <v>6284800</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="H11" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.587</v>
+        <v>0.586</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.524</v>
+        <v>0.51</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -989,45 +986,3326 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>726400</v>
+        <v>5889500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H12" t="n">
-        <v>78.59</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+        <v>61.44</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.676</v>
+        <v>0.787</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2.31</v>
+        <v>0.714</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5787000</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H13" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0280</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MBN</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>5215000</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H14" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0470</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BFIELD</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>4101000</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H15" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3965900</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3896400</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H17" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3481900</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H18" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0037</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RGB</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>3381700</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H19" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>3334100</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H20" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3299600</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H21" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>-0.0738</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>3235200</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H22" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1.496</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UOADEV</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>3073000</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="H23" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2934000</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H24" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0113</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MMSV</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2893400</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="H25" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2777500</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H26" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2768300</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H27" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0278</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EDELTEQ</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2384200</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2337800</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H29" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>2320400</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>2097800</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>2.216</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0272</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TTVHB</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>2027500</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H32" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1836800</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H33" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1826800</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H34" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1805300</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H35" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>2.106</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1718700</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H36" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1680700</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H37" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1638600</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0268</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L&amp;PBHD</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1631400</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H39" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1541700</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H40" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1458500</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H41" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DATASONIC</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1417500</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H42" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1413100</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H43" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1380500</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H44" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5789</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LBS</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1380200</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H45" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1348800</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H46" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1281200</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H47" t="n">
+        <v>66.02</v>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1274300</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H48" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1190800</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H49" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1165500</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H50" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1157400</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>4.883</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1135800</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H52" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1112000</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H53" t="n">
+        <v>67.13</v>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>1081700</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H54" t="n">
+        <v>78.28</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1078600</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H55" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1021700</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H56" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1021200</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H57" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1001600</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H58" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>964800</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H59" t="n">
+        <v>57</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>4.669</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>921800</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>907000</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>47.22</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>-0.0342</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>862200</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H62" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>854200</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H63" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>831600</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H64" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>7.724</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>-0.0591</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>819600</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H65" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>2.261</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>772100</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H66" t="n">
+        <v>66.98</v>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>735600</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H67" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>728900</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H68" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>715200</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H69" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>714200</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H70" t="n">
+        <v>67.56</v>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>5.809</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>-0.0165</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>714200</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H71" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>703300</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H72" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>697600</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H73" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>661400</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H74" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>10.012</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>10.201</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>658100</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H75" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>-0.0219</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>631500</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H76" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>3.595</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>621500</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H77" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>607600</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H78" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>2.703</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>605800</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H79" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>594600</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>555700</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H81" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>532200</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>524500</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H83" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>512700</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>512600</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H85" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>7.571</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
+++ b/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-12" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,8 +82,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>108738600</v>
+        <v>115896800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H2" t="n">
         <v>23.54</v>
@@ -597,27 +597,27 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>46802700</v>
+        <v>75464700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.77</v>
+        <v>1.24</v>
       </c>
       <c r="H3" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.285</v>
+        <v>0.284</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.247</v>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-0.1543</v>
+        <v>0.18</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>16439700</v>
+        <v>36074500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>4.25</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="n">
-        <v>24.01</v>
+        <v>60.1</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.87</v>
+        <v>0.168</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.015</v>
+        <v>0.133</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0.0095</v>
+        <v>1.59</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-0.1543</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>12813100</v>
+        <v>22535100</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.48</v>
+        <v>5.82</v>
       </c>
       <c r="H5" t="n">
-        <v>76.25</v>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.01</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1.658</v>
+        <v>2.015</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-0.009599999999999999</v>
+        <v>2.12</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11024500</v>
+        <v>20301800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="H6" t="n">
-        <v>60.66</v>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.493</v>
+        <v>1.849</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.48</v>
+        <v>1.658</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,28 +768,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10790600</v>
+        <v>15666200</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="H7" t="n">
-        <v>60.1</v>
+        <v>50.73</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.168</v>
+        <v>0.196</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.133</v>
+        <v>0.184</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0361</v>
+        <v>0.515</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9451700</v>
+        <v>13982900</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
       <c r="H8" t="n">
-        <v>69.26000000000001</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
+        <v>60.66</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.649</v>
+        <v>0.493</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2.511</v>
+        <v>0.48</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,33 +858,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>2.83</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9311200</v>
+        <v>12605800</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+        <v>0.71</v>
+      </c>
+      <c r="H9" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>2.511</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
@@ -896,40 +903,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LUSTER</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.025</v>
+        <v>0.25</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6775500</v>
+        <v>11710500</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H10" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.028</v>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
@@ -941,39 +941,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>-0.008</v>
+        <v>0.835</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6284800</v>
+        <v>9992100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="H11" t="n">
-        <v>68.95999999999999</v>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
+        <v>61.44</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.586</v>
+        <v>0.787</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.51</v>
+        <v>0.714</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,39 +986,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>-0.0118</v>
+        <v>0.615</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5889500</v>
+        <v>9438100</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="H12" t="n">
-        <v>61.44</v>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.787</v>
+        <v>0.585</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.714</v>
+        <v>0.51</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1040,27 +1040,27 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.0159</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5787000</v>
+        <v>7522300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="H13" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
+        <v>64.23</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.587</v>
+        <v>0.586</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0.524</v>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>LUSTER</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.155</v>
+        <v>0.025</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5215000</v>
+        <v>6875500</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.63</v>
+        <v>1.27</v>
       </c>
       <c r="H14" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.7</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.154</v>
+        <v>0.026</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.152</v>
+        <v>0.028</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,36 +1121,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4101000</v>
+        <v>5460400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.35</v>
+        <v>0.92</v>
       </c>
       <c r="H15" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+        <v>71.34</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.275</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1162,40 +1166,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3965900</v>
+        <v>5413500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H16" t="n">
-        <v>53.81</v>
+        <v>47.36</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0.184</v>
-      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1207,39 +1207,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-0.023</v>
+        <v>0.48</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3896400</v>
+        <v>5234700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.17</v>
+        <v>1.54</v>
       </c>
       <c r="H17" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
+        <v>80.19</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.411</v>
+        <v>0.37</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1252,39 +1252,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.39</v>
+        <v>0.155</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3481900</v>
+        <v>5215000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.09</v>
+        <v>2.63</v>
       </c>
       <c r="H18" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
+        <v>52.49</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.361</v>
+        <v>0.154</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.243</v>
+        <v>0.152</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1297,39 +1297,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.295</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3381700</v>
+        <v>4885900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>75.02</v>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
+        <v>57.36</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.208</v>
+        <v>0.28</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.205</v>
+        <v>0.303</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1342,39 +1342,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3334100</v>
+        <v>4789800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="H20" t="n">
-        <v>57.36</v>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
+        <v>65.5</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.303</v>
+        <v>0.243</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1387,39 +1387,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.465</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3299600</v>
+        <v>4700100</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="H21" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.59</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.773</v>
+        <v>0.541</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.716</v>
+        <v>0.737</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1432,39 +1432,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>-0.0738</v>
+        <v>0.42</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3235200</v>
+        <v>4637500</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.84</v>
+        <v>0.2</v>
       </c>
       <c r="H22" t="n">
-        <v>26.89</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.03</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.496</v>
+        <v>0.411</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.613</v>
+        <v>0.35</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1477,39 +1477,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UOADEV</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>0.805</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3073000</v>
+        <v>4458900</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>14.52</v>
+        <v>0.32</v>
       </c>
       <c r="H23" t="n">
-        <v>22.66</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.557</v>
+        <v>0.772</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.614</v>
+        <v>0.716</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1522,39 +1522,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.375</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.026</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2934000</v>
+        <v>4311500</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H24" t="n">
-        <v>68.55</v>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
+        <v>63.01</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.291</v>
+        <v>0.356</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.275</v>
+        <v>0.323</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1567,39 +1567,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0159</v>
+        <v>0.515</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-0.055</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2893400</v>
+        <v>4171200</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>10.56</v>
+        <v>0.75</v>
       </c>
       <c r="H25" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.26</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.295</v>
+        <v>0.585</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.297</v>
+        <v>0.638</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1612,28 +1612,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0381</v>
+        <v>1.38</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-0.0738</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2777500</v>
+        <v>4157700</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.17</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
-        <v>59.29</v>
+        <v>26.89</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.515</v>
+        <v>1.496</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.441</v>
+        <v>1.613</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1672,15 +1672,15 @@
         <v>0.013</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2768300</v>
+        <v>4030300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="H27" t="n">
         <v>53.34</v>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1702,39 +1702,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0538</v>
+        <v>2.12</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2384200</v>
+        <v>3794400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="H28" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.24</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.371</v>
+        <v>2.216</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.352</v>
+        <v>2.217</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1747,39 +1747,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>-0.0275</v>
+        <v>0.22</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2337800</v>
+        <v>3551100</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.42</v>
+        <v>3.89</v>
       </c>
       <c r="H29" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.02</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.586</v>
+        <v>0.208</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.638</v>
+        <v>0.205</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1792,28 +1792,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>-0.0211</v>
+        <v>0.545</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0381</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2320400</v>
+        <v>3528300</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="H30" t="n">
-        <v>25.59</v>
+        <v>59.29</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.541</v>
+        <v>0.515</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.737</v>
+        <v>0.441</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1837,39 +1837,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>-0.0185</v>
+        <v>0.82</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2097800</v>
+        <v>3499300</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="H31" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.216</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.217</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1882,39 +1882,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>-0.0182</v>
+        <v>0.725</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.0203</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2027500</v>
+        <v>3448900</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.91</v>
+        <v>0.41</v>
       </c>
       <c r="H32" t="n">
-        <v>57.92</v>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
+        <v>57.3</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.252</v>
+        <v>0.696</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.254</v>
+        <v>0.681</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1927,39 +1927,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>-0.0125</v>
+        <v>0.22</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1836800</v>
+        <v>3389600</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="H33" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.58</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.781</v>
+        <v>0.246</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.773</v>
+        <v>0.301</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1972,39 +1972,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.74</v>
+        <v>0.125</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1826800</v>
+        <v>3208800</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.22</v>
+        <v>0.68</v>
       </c>
       <c r="H34" t="n">
-        <v>61.02</v>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
+        <v>55.22</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.698</v>
+        <v>0.122</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2017,39 +2017,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.305</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-0.0317</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1805300</v>
+        <v>3186000</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.09</v>
+        <v>11.63</v>
       </c>
       <c r="H35" t="n">
-        <v>57.43</v>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
+        <v>56.58</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.106</v>
+        <v>0.294</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2.086</v>
+        <v>0.297</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2062,39 +2062,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.615</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1718700</v>
+        <v>3080900</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1.12</v>
+        <v>0.29</v>
       </c>
       <c r="H36" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.86</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.421</v>
+        <v>0.612</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.44</v>
+        <v>0.611</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2107,39 +2107,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>UOADEV</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>-0.0159</v>
+        <v>1.51</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1680700</v>
+        <v>3078000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.16</v>
+        <v>14.54</v>
       </c>
       <c r="H37" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.9</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.613</v>
+        <v>1.558</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.612</v>
+        <v>1.614</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2152,39 +2152,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>0</v>
+        <v>2.15</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1638600</v>
+        <v>3076800</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="H38" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
+        <v>57.43</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>2.106</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>2.086</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2197,39 +2197,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.04</v>
+        <v>0.265</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1631400</v>
+        <v>2758200</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.79</v>
+        <v>1.24</v>
       </c>
       <c r="H39" t="n">
-        <v>82.25</v>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
+        <v>55.66</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.212</v>
+        <v>0.252</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.174</v>
+        <v>0.254</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2242,39 +2242,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>-0.0034</v>
+        <v>0.79</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1541700</v>
+        <v>2542100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="H40" t="n">
-        <v>77.43000000000001</v>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+        <v>53.58</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.675</v>
+        <v>0.781</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.31</v>
+        <v>0.773</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2287,28 +2287,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>4.64</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0153</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1458500</v>
+        <v>2441800</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="H41" t="n">
-        <v>33.08</v>
+        <v>38.75</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.247</v>
+        <v>4.714</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.301</v>
+        <v>4.883</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2332,39 +2332,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>-0.0167</v>
+        <v>2.93</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1417500</v>
+        <v>2391500</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="H42" t="n">
-        <v>52.19</v>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
+        <v>76.3</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.292</v>
+        <v>2.674</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.281</v>
+        <v>2.309</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2377,39 +2377,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>0.49</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1413100</v>
+        <v>2353100</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="H43" t="n">
-        <v>86.70999999999999</v>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.76</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.521</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.494</v>
+        <v>0.569</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2431,21 +2431,21 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0139</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1380500</v>
+        <v>2275900</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H44" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
+        <v>62.19</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2467,28 +2467,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1380200</v>
+        <v>2205800</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.13</v>
+        <v>0.28</v>
       </c>
       <c r="H45" t="n">
-        <v>38.45</v>
+        <v>54.61</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.385</v>
+        <v>0.523</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.395</v>
+        <v>0.531</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2512,39 +2512,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1348800</v>
+        <v>2177000</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H46" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.69</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.522</v>
+        <v>0.675</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.57</v>
+        <v>0.611</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2557,39 +2557,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>-0.013</v>
+        <v>0.945</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1281200</v>
+        <v>1975600</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H47" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.98</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.357</v>
+        <v>0.96</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.323</v>
+        <v>0.826</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2602,39 +2602,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0194</v>
+        <v>0.32</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1274300</v>
+        <v>1971300</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="H48" t="n">
-        <v>65.61</v>
-      </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.76</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.72</v>
+        <v>0.326</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.695</v>
+        <v>0.339</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2647,39 +2647,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1190800</v>
+        <v>1940400</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H49" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.524</v>
+        <v>4.932</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.531</v>
+        <v>4.669</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2692,39 +2692,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0.0186</v>
+        <v>1.13</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1165500</v>
+        <v>1938100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="H50" t="n">
-        <v>62.72</v>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.775</v>
+        <v>1.077</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.763</v>
+        <v>0.926</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2737,39 +2737,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4.64</v>
+        <v>0.255</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>0.0153</v>
+        <v>0.02</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1157400</v>
+        <v>1895400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="H51" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.26000000000001</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.714</v>
+        <v>0.211</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4.883</v>
+        <v>0.174</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2782,39 +2782,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>-0.0616</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1135800</v>
+        <v>1892500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="H52" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.26000000000001</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.338</v>
+        <v>0.537</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.344</v>
+        <v>0.449</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2827,39 +2827,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1112000</v>
+        <v>1791100</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.12</v>
+        <v>0.88</v>
       </c>
       <c r="H53" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
+        <v>60.82</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.078</v>
+        <v>0.774</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.926</v>
+        <v>0.762</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2872,39 +2872,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>-0.0164</v>
+        <v>6.82</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1081700</v>
+        <v>1775000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1.13</v>
+        <v>0.36</v>
       </c>
       <c r="H54" t="n">
-        <v>78.28</v>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
+        <v>66.70999999999999</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.269</v>
+        <v>5.933</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.266</v>
+        <v>5.808</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2917,28 +2917,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1078600</v>
+        <v>1719900</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.15</v>
+        <v>1.12</v>
       </c>
       <c r="H55" t="n">
-        <v>37.21</v>
+        <v>39.23</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.288</v>
+        <v>0.421</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.307</v>
+        <v>0.44</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2962,39 +2962,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0092</v>
+        <v>0.775</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1021700</v>
+        <v>1702600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="H56" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.64</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.58</v>
+        <v>0.718</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.621</v>
+        <v>0.695</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3007,28 +3007,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>-0.0109</v>
+        <v>7.3</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1021200</v>
+        <v>1659300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="H57" t="n">
-        <v>54.32</v>
+        <v>33.89</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.908</v>
+        <v>7.608</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.865</v>
+        <v>7.723</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3052,39 +3052,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>-0.0185</v>
+        <v>1.01</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1001600</v>
+        <v>1647200</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.22</v>
+        <v>0.48</v>
       </c>
       <c r="H58" t="n">
-        <v>61.04</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.70999999999999</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.252</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.221</v>
+        <v>0.494</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3097,39 +3097,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>-0.0157</v>
+        <v>0.885</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.0221</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>964800</v>
+        <v>1607300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.04</v>
+        <v>0.47</v>
       </c>
       <c r="H59" t="n">
-        <v>57</v>
-      </c>
-      <c r="I59" s="8" t="inlineStr">
+        <v>64.38</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4.933</v>
+        <v>0.832</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.669</v>
+        <v>0.763</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3142,39 +3142,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.725</v>
+        <v>0.215</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.0488</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>921800</v>
+        <v>1546500</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.1</v>
+        <v>1.51</v>
       </c>
       <c r="H60" t="n">
-        <v>64.34</v>
-      </c>
-      <c r="I60" s="8" t="inlineStr">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.677</v>
+        <v>0.204</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.612</v>
+        <v>0.211</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3187,39 +3187,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>-0.0187</v>
+        <v>0.865</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>907000</v>
+        <v>1544000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H61" t="n">
-        <v>47.22</v>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
+        <v>46.92</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.07</v>
+        <v>0.868</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.038</v>
+        <v>0.869</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3232,39 +3232,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>-0.0342</v>
+        <v>0.295</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>862200</v>
+        <v>1494200</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="H62" t="n">
-        <v>80.78</v>
-      </c>
-      <c r="I62" s="8" t="inlineStr">
+        <v>52.19</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.539</v>
+        <v>0.292</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.45</v>
+        <v>0.281</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3277,39 +3277,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>854200</v>
+        <v>1486300</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
+        <v>55.23</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.162</v>
+        <v>1.163</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1.122</v>
+        <v>1.17</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3322,39 +3322,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0083</v>
+        <v>1.18</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>831600</v>
+        <v>1475900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="H64" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.25</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.61</v>
+        <v>1.037</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>7.724</v>
+        <v>0.87</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3367,28 +3367,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E65" s="9" t="n">
-        <v>-0.0591</v>
+        <v>0.37</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>819600</v>
+        <v>1465800</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1.67</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>33.94</v>
+        <v>52.46</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.261</v>
+        <v>0.368</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.22</v>
+        <v>0.368</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3412,39 +3412,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E66" s="9" t="n">
-        <v>-0.011</v>
+        <v>0.22</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>772100</v>
+        <v>1446000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.22</v>
+        <v>0.86</v>
       </c>
       <c r="H66" t="n">
-        <v>66.98</v>
-      </c>
-      <c r="I66" s="8" t="inlineStr">
+        <v>58.47</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.833</v>
+        <v>0.212</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.763</v>
+        <v>0.19</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3457,28 +3457,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.38</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>735600</v>
+        <v>1398200</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.28</v>
+        <v>1.14</v>
       </c>
       <c r="H67" t="n">
-        <v>48.56</v>
+        <v>38.45</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.638</v>
+        <v>0.385</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.612</v>
+        <v>0.395</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3502,40 +3502,36 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E68" s="9" t="n">
-        <v>-0.0052</v>
+        <v>0.34</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>728900</v>
+        <v>1391000</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H68" t="n">
-        <v>54.43</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>0.827</v>
-      </c>
+        <v>66.19</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
     </row>
@@ -3547,39 +3543,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>2.07</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0591</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>715200</v>
+        <v>1360400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.37</v>
+        <v>2.76</v>
       </c>
       <c r="H69" t="n">
-        <v>53.07</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.94</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.277</v>
+        <v>2.261</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.318</v>
+        <v>2.22</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3592,39 +3588,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0177</v>
+        <v>7.2</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>714200</v>
+        <v>1329500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H70" t="n">
-        <v>67.56</v>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.32</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>5.94</v>
+        <v>7.567</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>5.809</v>
+        <v>8.069000000000001</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3646,19 +3642,19 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E71" s="9" t="n">
-        <v>-0.0165</v>
+        <v>1.2</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>714200</v>
+        <v>1298500</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.32</v>
+        <v>0.58</v>
       </c>
       <c r="H71" t="n">
-        <v>31.53</v>
+        <v>32.6</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3666,10 +3662,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.28</v>
+        <v>1.281</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.309</v>
+        <v>1.31</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3682,39 +3678,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E72" s="9" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.14</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>703300</v>
+        <v>1260300</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H72" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.601</v>
+        <v>1.161</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.583</v>
+        <v>1.122</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3727,39 +3723,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>697600</v>
+        <v>1258100</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="H73" t="n">
-        <v>66.89</v>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.495</v>
+        <v>0.554</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.481</v>
+        <v>0.498</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3781,19 +3777,19 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9.92</v>
+        <v>9.9</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0092</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>661400</v>
+        <v>1241500</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H74" t="n">
-        <v>40.74</v>
+        <v>39.21</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3801,7 +3797,7 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>10.012</v>
+        <v>10.01</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>10.201</v>
@@ -3817,39 +3813,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E75" s="9" t="n">
-        <v>-0.005699999999999999</v>
+        <v>5.63</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>658100</v>
+        <v>1221100</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H75" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.868</v>
+        <v>5.644</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.869</v>
+        <v>5.338</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3862,39 +3858,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>-0.0219</v>
+        <v>1.28</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>631500</v>
+        <v>1198000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.06</v>
+        <v>0.62</v>
       </c>
       <c r="H76" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.77</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>3.595</v>
+        <v>1.275</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.783</v>
+        <v>1.318</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3907,39 +3903,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E77" s="9" t="n">
-        <v>-0.0161</v>
+        <v>0.33</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>621500</v>
+        <v>1190000</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H77" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.04</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.165</v>
+        <v>0.338</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.17</v>
+        <v>0.344</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3952,28 +3948,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>1.76</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>607600</v>
+        <v>1185100</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="H78" t="n">
-        <v>56.5</v>
+        <v>50.14</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3981,10 +3977,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.8</v>
+        <v>1.755</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.703</v>
+        <v>1.778</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3997,39 +3993,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.014</v>
+        <v>0.295</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>605800</v>
+        <v>1181900</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.32</v>
+        <v>1.23</v>
       </c>
       <c r="H79" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.733</v>
+        <v>0.269</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.748</v>
+        <v>0.266</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4042,39 +4038,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.0054</v>
+        <v>1.04</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>594600</v>
+        <v>1169000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H80" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.74</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.913</v>
+        <v>1.069</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.963</v>
+        <v>1.038</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4087,39 +4083,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>-0.0189</v>
+        <v>0.525</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>555700</v>
+        <v>1164600</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.13</v>
+        <v>0.59</v>
       </c>
       <c r="H81" t="n">
-        <v>46.17</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.38</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.791</v>
+        <v>0.494</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.806</v>
+        <v>0.481</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4132,39 +4128,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0</v>
+        <v>0.91</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>532200</v>
+        <v>1103600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="H82" t="n">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.32</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.555</v>
+        <v>0.908</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.498</v>
+        <v>0.865</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4177,39 +4173,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E83" s="9" t="n">
-        <v>-0.008</v>
+        <v>0.47</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>524500</v>
+        <v>1100400</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.06</v>
+        <v>0.59</v>
       </c>
       <c r="H83" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.34</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.281</v>
+        <v>0.462</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.379</v>
+        <v>0.461</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4222,39 +4218,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.005600000000000001</v>
+        <v>2.04</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>-0.0239</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>512700</v>
+        <v>1093500</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
       <c r="H84" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.96</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.758</v>
+        <v>2.057</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.779</v>
+        <v>2.083</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4267,28 +4263,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.265</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>512600</v>
+        <v>1088100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="H85" t="n">
-        <v>26.35</v>
+        <v>61.04</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4296,16 +4292,1501 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>7.571</v>
+        <v>0.252</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>8.07</v>
+        <v>0.221</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>1086600</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H86" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1066900</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H87" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>1047800</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H88" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>1047500</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>1004000</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H90" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>991400</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H91" t="n">
+        <v>72.19</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>979100</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>-0.0242</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>965900</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H93" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>965700</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H94" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>3.597</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>793300</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H95" t="n">
+        <v>46</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>783900</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H96" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>767500</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>746900</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H98" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>745900</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H99" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>743400</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H100" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>2.801</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>2.703</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>724400</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H101" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>716900</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H102" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>707400</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>81.06999999999999</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>698200</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H104" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>3.382</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>672400</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H105" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>637800</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H106" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>3.995</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>3.468</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>636400</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H107" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>631300</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>605800</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H109" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>573100</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H110" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>567900</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H111" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>RCECAP</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>567400</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>562800</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H113" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>543600</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H114" t="n">
+        <v>61.84</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>533800</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H115" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>5.518</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>5.374</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>527300</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H116" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>13.022</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>13.544</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>516400</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H117" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>510000</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H118" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M85"/>
+  <autoFilter ref="A1:M118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
+++ b/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-12" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>115896800</v>
+        <v>118532000</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0.27</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.058</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>75464700</v>
+        <v>91900600</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="H3" t="n">
-        <v>70.48999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.284</v>
+        <v>0.283</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.247</v>
+        <v>0.246</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>36074500</v>
+        <v>36664500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>60.1</v>
+        <v>57.25</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.1543</v>
+        <v>-0.1649</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>22535100</v>
+        <v>28618500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>5.82</v>
+        <v>7.39</v>
       </c>
       <c r="H5" t="n">
-        <v>24.01</v>
+        <v>23.29</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.87</v>
+        <v>1.868</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>2.015</v>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20301800</v>
+        <v>22065200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H6" t="n">
-        <v>75.90000000000001</v>
+        <v>76.25</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.849</v>
+        <v>1.85</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1.658</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.195</v>
+        <v>0.19</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.025</v>
+        <v>-0.05</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15666200</v>
+        <v>15753400</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.68</v>
       </c>
       <c r="H7" t="n">
-        <v>50.73</v>
+        <v>47.99</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>-0.009599999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13982900</v>
+        <v>15038300</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H8" t="n">
         <v>60.66</v>
@@ -858,40 +858,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0217</v>
+        <v>0.25</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12605800</v>
+        <v>13285200</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H9" t="n">
-        <v>67.42</v>
+        <v>0.38</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>2.645</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>2.511</v>
-      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
@@ -903,33 +896,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11710500</v>
+        <v>13199500</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
+      </c>
+      <c r="H10" t="n">
+        <v>66.93000000000001</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+      <c r="J10" s="2" t="n">
+        <v>2.644</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>2.51</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
@@ -941,28 +941,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>-0.0118</v>
+        <v>0.315</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.05</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9992100</v>
+        <v>13024900</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.14</v>
+        <v>2.19</v>
       </c>
       <c r="H11" t="n">
-        <v>61.44</v>
+        <v>73.67</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.787</v>
+        <v>0.292</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.714</v>
+        <v>0.276</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>-0.016</v>
+        <v>0.625</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9438100</v>
+        <v>12955900</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>66.51000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.585</v>
+        <v>0.586</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0.51</v>
@@ -1031,28 +1031,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0.0159</v>
+        <v>0.825</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-0.0237</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7522300</v>
+        <v>11616000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="H13" t="n">
-        <v>64.23</v>
+        <v>59.46</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.586</v>
+        <v>0.786</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.524</v>
+        <v>0.713</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LUSTER</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6875500</v>
+        <v>10616200</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.27</v>
+        <v>0.58</v>
       </c>
       <c r="H14" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.61</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.026</v>
+        <v>0.585</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.028</v>
+        <v>0.523</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,28 +1121,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.42</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5460400</v>
+        <v>7181300</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.92</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
-        <v>71.34</v>
+        <v>56.03</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.292</v>
+        <v>0.411</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.275</v>
+        <v>0.35</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,36 +1166,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5413500</v>
+        <v>7034900</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.46</v>
+        <v>0.19</v>
       </c>
       <c r="H16" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+        <v>70.36</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.243</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1207,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>LUSTER</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.0323</v>
+        <v>0.025</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5234700</v>
+        <v>6875500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="H17" t="n">
-        <v>80.19</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.7</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.37</v>
+        <v>0.026</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.352</v>
+        <v>0.028</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1252,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0421</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5215000</v>
+        <v>6431500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.63</v>
+        <v>0.17</v>
       </c>
       <c r="H18" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.62</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.154</v>
+        <v>0.54</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.152</v>
+        <v>0.737</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1297,28 +1301,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>0.475</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0215</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4885900</v>
+        <v>6114900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="H19" t="n">
-        <v>57.36</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1326,10 +1330,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.28</v>
+        <v>0.369</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.303</v>
+        <v>0.352</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1342,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>-0.0256</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4789800</v>
+        <v>5761000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.13</v>
+        <v>1.04</v>
       </c>
       <c r="H20" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.57</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.36</v>
+        <v>0.584</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.243</v>
+        <v>0.638</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1387,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.465</v>
+        <v>1.39</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>-0.0211</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4700100</v>
+        <v>5567100</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.12</v>
+        <v>3.16</v>
       </c>
       <c r="H21" t="n">
-        <v>25.59</v>
+        <v>27.73</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1416,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.541</v>
+        <v>1.497</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.737</v>
+        <v>1.613</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1432,40 +1436,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-0.0345</v>
+        <v>0.47</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4637500</v>
+        <v>5425000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="H22" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0.35</v>
-      </c>
+        <v>47.36</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1477,28 +1477,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>-0.0062</v>
+        <v>0.78</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.013</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4458900</v>
+        <v>5380300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H23" t="n">
-        <v>58.16</v>
+        <v>53.34</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.772</v>
+        <v>0.775</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.716</v>
+        <v>0.775</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1522,28 +1522,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>-0.026</v>
+        <v>0.155</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4311500</v>
+        <v>5215000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.51</v>
+        <v>2.63</v>
       </c>
       <c r="H24" t="n">
-        <v>63.01</v>
+        <v>52.49</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.356</v>
+        <v>0.154</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.323</v>
+        <v>0.152</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1567,39 +1567,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>-0.055</v>
+        <v>0.295</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4171200</v>
+        <v>5127400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="H25" t="n">
-        <v>27.26</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.36</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.585</v>
+        <v>0.28</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.638</v>
+        <v>0.303</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1612,28 +1612,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.38</v>
+        <v>0.02</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>-0.0738</v>
+        <v>-0.2</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4157700</v>
+        <v>5022000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2.36</v>
+        <v>0.27</v>
       </c>
       <c r="H26" t="n">
-        <v>26.89</v>
+        <v>28.3</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.496</v>
+        <v>0.024</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.613</v>
+        <v>0.024</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1657,28 +1657,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.013</v>
+        <v>0.82</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4030300</v>
+        <v>4919200</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H27" t="n">
-        <v>53.34</v>
+        <v>58.27</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1702,39 +1702,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>-0.0185</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3794400</v>
+        <v>4714000</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.12</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.216</v>
+        <v>0.773</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.217</v>
+        <v>0.716</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1747,28 +1747,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.375</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>-0.026</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3551100</v>
+        <v>4450600</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3.89</v>
+        <v>0.53</v>
       </c>
       <c r="H29" t="n">
-        <v>75.02</v>
+        <v>63.01</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.208</v>
+        <v>0.356</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.205</v>
+        <v>0.323</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1792,39 +1792,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.31</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3528300</v>
+        <v>4366000</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H30" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.85</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.515</v>
+        <v>0.306</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.441</v>
+        <v>0.296</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1837,39 +1837,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3499300</v>
+        <v>4240800</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.61</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.225</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.241</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1882,28 +1882,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.725</v>
+        <v>0.62</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.0203</v>
+        <v>-0.0159</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3448900</v>
+        <v>4240600</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="H32" t="n">
-        <v>57.3</v>
+        <v>54.39</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.696</v>
+        <v>0.613</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.681</v>
+        <v>0.612</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1927,28 +1927,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.22</v>
+        <v>2.12</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>-0.0222</v>
+        <v>-0.0185</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3389600</v>
+        <v>3900000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="H33" t="n">
-        <v>31.58</v>
+        <v>40.24</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.246</v>
+        <v>2.216</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.301</v>
+        <v>2.217</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1972,39 +1972,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3208800</v>
+        <v>3898400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="H34" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.49</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.122</v>
+        <v>0.514</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.125</v>
+        <v>0.441</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2017,28 +2017,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>-0.0317</v>
+        <v>2.14</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3186000</v>
+        <v>3884300</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>11.63</v>
+        <v>0.2</v>
       </c>
       <c r="H35" t="n">
-        <v>56.58</v>
+        <v>56.18</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.294</v>
+        <v>2.105</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.297</v>
+        <v>2.085</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2062,28 +2062,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.615</v>
+        <v>0.725</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>-0.0238</v>
+        <v>-0.0203</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3080900</v>
+        <v>3810600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="H36" t="n">
-        <v>51.86</v>
+        <v>57.3</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.612</v>
+        <v>0.696</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.611</v>
+        <v>0.681</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2107,39 +2107,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UOADEV</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.51</v>
+        <v>0.22</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0233</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3078000</v>
+        <v>3551100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>14.54</v>
+        <v>3.89</v>
       </c>
       <c r="H37" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.02</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.558</v>
+        <v>0.208</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.614</v>
+        <v>0.205</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2152,28 +2152,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.15</v>
+        <v>0.365</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0139</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3076800</v>
+        <v>3546200</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H38" t="n">
-        <v>57.43</v>
+        <v>62.19</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.106</v>
+        <v>0.346</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.086</v>
+        <v>0.326</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2197,39 +2197,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>-0.0364</v>
+        <v>4.65</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2758200</v>
+        <v>3500400</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1.24</v>
+        <v>0.22</v>
       </c>
       <c r="H39" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.92</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.252</v>
+        <v>4.715</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.254</v>
+        <v>4.883</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2242,39 +2242,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.79</v>
+        <v>0.22</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>-0.0125</v>
+        <v>-0.0222</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2542100</v>
+        <v>3465500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="H40" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.58</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.781</v>
+        <v>0.246</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.773</v>
+        <v>0.301</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2287,39 +2287,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.0153</v>
+        <v>0.31</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2441800</v>
+        <v>3251000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.15</v>
+        <v>11.87</v>
       </c>
       <c r="H41" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.79</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.714</v>
+        <v>0.294</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4.883</v>
+        <v>0.297</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2332,28 +2332,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>-0.0068</v>
+        <v>0.125</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2391500</v>
+        <v>3228800</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H42" t="n">
-        <v>76.3</v>
+        <v>55.22</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.674</v>
+        <v>0.122</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.309</v>
+        <v>0.125</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2377,39 +2377,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-0.02</v>
+        <v>-0.0278</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2353100</v>
+        <v>3182400</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H43" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.5</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.521</v>
+        <v>0.675</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.569</v>
+        <v>0.611</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2422,28 +2422,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0038</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>ARTRONIQ</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.365</v>
+        <v>0.145</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.0139</v>
+        <v>0.0357</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2275900</v>
+        <v>3144500</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.3</v>
+        <v>9.66</v>
       </c>
       <c r="H44" t="n">
-        <v>62.19</v>
+        <v>79.14</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.346</v>
+        <v>0.134</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.326</v>
+        <v>0.132</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2467,28 +2467,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>UOADEV</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>-0.009300000000000001</v>
+        <v>1.51</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2205800</v>
+        <v>3078000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.28</v>
+        <v>14.54</v>
       </c>
       <c r="H45" t="n">
-        <v>54.61</v>
+        <v>27.9</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.523</v>
+        <v>1.558</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.531</v>
+        <v>1.614</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2512,39 +2512,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>-0.0208</v>
+        <v>0.17</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2177000</v>
+        <v>3053100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="H46" t="n">
-        <v>59.69</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.52</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.675</v>
+        <v>0.184</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.611</v>
+        <v>0.197</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2557,28 +2557,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>-0.0207</v>
+        <v>0.725</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.014</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1975600</v>
+        <v>3016800</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.25</v>
+        <v>1.61</v>
       </c>
       <c r="H47" t="n">
-        <v>51.98</v>
+        <v>46.48</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.96</v>
+        <v>0.733</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.826</v>
+        <v>0.748</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2602,39 +2602,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0125</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1971300</v>
+        <v>2937700</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H48" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.58</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.326</v>
+        <v>0.781</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.339</v>
+        <v>0.773</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2647,28 +2647,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5</v>
+        <v>0.265</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>-0.0177</v>
+        <v>-0.0364</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1940400</v>
+        <v>2881800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.08</v>
+        <v>1.3</v>
       </c>
       <c r="H49" t="n">
-        <v>56.45</v>
+        <v>55.66</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4.932</v>
+        <v>0.252</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4.669</v>
+        <v>0.254</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2692,28 +2692,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1938100</v>
+        <v>2554700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
       <c r="H50" t="n">
-        <v>64.90000000000001</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.077</v>
+        <v>0.211</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.926</v>
+        <v>0.174</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2737,28 +2737,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1895400</v>
+        <v>2549300</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="H51" t="n">
-        <v>81.26000000000001</v>
+        <v>55.23</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.211</v>
+        <v>1.163</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.174</v>
+        <v>1.17</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2782,28 +2782,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>5</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>-0.0616</v>
+        <v>-0.0177</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1892500</v>
+        <v>2522300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="H52" t="n">
-        <v>76.26000000000001</v>
+        <v>56.45</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.537</v>
+        <v>4.932</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.449</v>
+        <v>4.669</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2827,39 +2827,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0259</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1791100</v>
+        <v>2483800</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="H53" t="n">
-        <v>60.82</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.21</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.774</v>
+        <v>0.959</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.762</v>
+        <v>0.826</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2872,39 +2872,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>6.82</v>
+        <v>7.3</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1775000</v>
+        <v>2460000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="H54" t="n">
-        <v>66.70999999999999</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.89</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>5.933</v>
+        <v>7.608</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.808</v>
+        <v>7.723</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2917,28 +2917,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.04480000000000001</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>2448000</v>
+      </c>
+      <c r="G55" s="5" t="n">
         <v>0.41</v>
       </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>1719900</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="H55" t="n">
-        <v>39.23</v>
+        <v>46.76</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.421</v>
+        <v>0.326</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.44</v>
+        <v>0.339</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2962,28 +2962,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1702600</v>
+        <v>2410600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="H56" t="n">
-        <v>63.64</v>
+        <v>76.3</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.718</v>
+        <v>2.674</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.695</v>
+        <v>2.309</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3007,39 +3007,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1659300</v>
+        <v>2366100</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>0.12</v>
       </c>
       <c r="H57" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.92</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7.608</v>
+        <v>0.868</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>7.723</v>
+        <v>0.869</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3052,28 +3052,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>1.04</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1647200</v>
+        <v>2360900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
       <c r="H58" t="n">
-        <v>86.70999999999999</v>
+        <v>45.74</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.069</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.494</v>
+        <v>1.038</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3097,39 +3097,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.885</v>
+        <v>0.495</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>-0.0221</v>
+        <v>-0.01</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1607300</v>
+        <v>2357100</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="H59" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.1</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.832</v>
+        <v>0.522</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.763</v>
+        <v>0.57</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3142,39 +3142,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0.0488</v>
+        <v>0.53</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1546500</v>
+        <v>2348000</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1.51</v>
+        <v>0.3</v>
       </c>
       <c r="H60" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.71</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.204</v>
+        <v>0.523</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.211</v>
+        <v>0.531</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3187,28 +3187,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.865</v>
+        <v>0.705</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0342</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1544000</v>
+        <v>2343200</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.08</v>
+        <v>0.46</v>
       </c>
       <c r="H61" t="n">
-        <v>46.92</v>
+        <v>80.78</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.868</v>
+        <v>0.539</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.869</v>
+        <v>0.45</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3232,28 +3232,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>-0.0167</v>
+        <v>0.825</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1494200</v>
+        <v>2317200</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.12</v>
+        <v>1.14</v>
       </c>
       <c r="H62" t="n">
-        <v>52.19</v>
+        <v>63.6</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.292</v>
+        <v>0.776</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.281</v>
+        <v>0.763</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3277,28 +3277,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.2</v>
+        <v>0.87</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.0323</v>
+        <v>-0.0387</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1486300</v>
+        <v>2161400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
       <c r="H63" t="n">
-        <v>55.23</v>
+        <v>60.83</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.163</v>
+        <v>0.83</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1.17</v>
+        <v>0.762</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3322,28 +3322,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0175</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1475900</v>
+        <v>2076100</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="H64" t="n">
-        <v>69.25</v>
+        <v>62.8</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.037</v>
+        <v>1.076</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.87</v>
+        <v>0.926</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3367,28 +3367,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>-0.0133</v>
+        <v>0.2</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1465800</v>
+        <v>2023200</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.22</v>
+        <v>0.49</v>
       </c>
       <c r="H65" t="n">
-        <v>52.46</v>
+        <v>42.8</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.368</v>
+        <v>0.206</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.368</v>
+        <v>0.208</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3412,39 +3412,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1446000</v>
+        <v>2019800</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="H66" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.46</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.212</v>
+        <v>0.368</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.19</v>
+        <v>0.368</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3457,39 +3457,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>6.83</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.0074</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1398200</v>
+        <v>1969400</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1.14</v>
+        <v>0.4</v>
       </c>
       <c r="H67" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.385</v>
+        <v>5.934</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.395</v>
+        <v>5.808</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3502,36 +3502,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.34</v>
+        <v>7.2</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>-0.0286</v>
+        <v>-0.0028</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1391000</v>
+        <v>1894600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H68" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n"/>
+        <v>24.32</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>7.567</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>8.069000000000001</v>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
     </row>
@@ -3543,39 +3547,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>-0.0591</v>
+        <v>0.78</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1360400</v>
+        <v>1865600</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>2.76</v>
+        <v>0.96</v>
       </c>
       <c r="H69" t="n">
-        <v>33.94</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.261</v>
+        <v>0.719</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2.22</v>
+        <v>0.695</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3588,28 +3592,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>7.2</v>
+        <v>1.14</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.0028</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1329500</v>
+        <v>1842500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H70" t="n">
-        <v>24.32</v>
+        <v>48.12</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3617,10 +3621,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>7.567</v>
+        <v>1.161</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>8.069000000000001</v>
+        <v>1.122</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3633,28 +3637,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.2</v>
+        <v>2.13</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>-0.0083</v>
+        <v>-0.0318</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1298500</v>
+        <v>1747400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.58</v>
+        <v>3.55</v>
       </c>
       <c r="H71" t="n">
-        <v>32.6</v>
+        <v>37.61</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3662,10 +3666,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.281</v>
+        <v>2.267</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.31</v>
+        <v>2.221</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3678,39 +3682,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0246</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1260300</v>
+        <v>1744200</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="H72" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.64</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.161</v>
+        <v>1.038</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1.122</v>
+        <v>0.871</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3723,39 +3727,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>-0.0165</v>
+        <v>0.41</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1258100</v>
+        <v>1719900</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.23</v>
+        <v>1.12</v>
       </c>
       <c r="H73" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.554</v>
+        <v>0.421</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.498</v>
+        <v>0.44</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3768,39 +3772,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0092</v>
+        <v>0.52</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1241500</v>
+        <v>1687200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.1</v>
+        <v>0.85</v>
       </c>
       <c r="H74" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.06</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>10.01</v>
+        <v>0.494</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>10.201</v>
+        <v>0.481</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3813,39 +3817,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>-0.0123</v>
+        <v>1.01</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1221100</v>
+        <v>1678700</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.09</v>
+        <v>0.49</v>
       </c>
       <c r="H75" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.70999999999999</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>5.644</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>5.338</v>
+        <v>0.494</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3858,28 +3862,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.28</v>
+        <v>0.215</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.0229</v>
+        <v>-0.0227</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1198000</v>
+        <v>1671600</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>49.77</v>
+        <v>54.98</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
@@ -3887,10 +3891,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.275</v>
+        <v>0.211</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.318</v>
+        <v>0.19</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3903,28 +3907,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.0154</v>
+        <v>5.63</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1190000</v>
+        <v>1648400</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="H77" t="n">
-        <v>39.04</v>
+        <v>51.65</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3932,10 +3936,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.338</v>
+        <v>5.644</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.344</v>
+        <v>5.338</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3948,39 +3952,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>-0.0112</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1185100</v>
+        <v>1617800</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H78" t="n">
-        <v>50.14</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.19</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.755</v>
+        <v>0.788</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.778</v>
+        <v>0.766</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3993,28 +3997,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>-0.0328</v>
+        <v>0.215</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1181900</v>
+        <v>1607700</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="H79" t="n">
-        <v>72.34999999999999</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
@@ -4022,10 +4026,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.269</v>
+        <v>0.204</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.266</v>
+        <v>0.211</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4038,28 +4042,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1.04</v>
+        <v>0.295</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-0.028</v>
+        <v>-0.0167</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1169000</v>
+        <v>1597000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="H80" t="n">
-        <v>45.74</v>
+        <v>52.19</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -4067,10 +4071,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.069</v>
+        <v>0.292</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1.038</v>
+        <v>0.281</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4083,39 +4087,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>-0.009399999999999999</v>
+        <v>9.94</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1164600</v>
+        <v>1595000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.59</v>
+        <v>0.12</v>
       </c>
       <c r="H81" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.19</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.494</v>
+        <v>10.014</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.481</v>
+        <v>10.201</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4128,39 +4132,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.91</v>
+        <v>0.6</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>-0.0109</v>
+        <v>-0.0083</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1103600</v>
+        <v>1532800</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H82" t="n">
-        <v>54.32</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.39</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.908</v>
+        <v>0.554</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.865</v>
+        <v>0.498</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4173,39 +4177,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>-0.0105</v>
+        <v>0.38</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1100400</v>
+        <v>1507800</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.59</v>
+        <v>1.23</v>
       </c>
       <c r="H83" t="n">
-        <v>54.34</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.45</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.462</v>
+        <v>0.385</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.461</v>
+        <v>0.395</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4218,28 +4222,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>2.04</v>
+        <v>0.405</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>-0.0239</v>
+        <v>-0.0241</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1093500</v>
+        <v>1488600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="H84" t="n">
-        <v>45.96</v>
+        <v>56.87</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -4247,10 +4251,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.057</v>
+        <v>0.388</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2.083</v>
+        <v>0.376</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4263,39 +4267,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.265</v>
+        <v>0.445</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>-0.0185</v>
+        <v>-0.0326</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1088100</v>
+        <v>1429100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="H85" t="n">
-        <v>61.04</v>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.65</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.252</v>
+        <v>0.451</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.221</v>
+        <v>0.428</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4308,40 +4312,36 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1086600</v>
+        <v>1414500</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H86" t="n">
-        <v>37.21</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0.307</v>
-      </c>
+        <v>66.19</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
     </row>
@@ -4353,39 +4353,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.0185</v>
+        <v>1.2</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1066900</v>
+        <v>1411800</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.16</v>
+        <v>0.63</v>
       </c>
       <c r="H87" t="n">
-        <v>43.76</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.6</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.668</v>
+        <v>1.281</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4398,28 +4398,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.22</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1047800</v>
+        <v>1406300</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="H88" t="n">
-        <v>37.75</v>
+        <v>40.88</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.581</v>
+        <v>0.231</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.621</v>
+        <v>0.234</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4443,28 +4443,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-0.0217</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1047500</v>
+        <v>1372300</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="H89" t="n">
-        <v>50.84</v>
+        <v>62.7</v>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.451</v>
+        <v>0.601</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.428</v>
+        <v>0.583</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4488,39 +4488,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>-0.0155</v>
+        <v>0.33</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1004000</v>
+        <v>1367900</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>0.26</v>
       </c>
       <c r="H90" t="n">
-        <v>61.12</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.04</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6</v>
+        <v>0.338</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.583</v>
+        <v>0.344</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4533,28 +4533,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>991400</v>
+        <v>1348500</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H91" t="n">
-        <v>72.19</v>
+        <v>43.76</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.788</v>
+        <v>1.668</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.766</v>
+        <v>1.78</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4578,28 +4578,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.28</v>
+        <v>0.235</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0208</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>979100</v>
+        <v>1341900</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="H92" t="n">
-        <v>43.38</v>
+        <v>46.24</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.319</v>
+        <v>0.241</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.308</v>
+        <v>0.249</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4623,39 +4623,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.605</v>
+        <v>3.57</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>-0.0242</v>
+        <v>-0.0246</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>965900</v>
+        <v>1320800</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="H93" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.99</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.614</v>
+        <v>3.594</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.608</v>
+        <v>2.782</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4668,39 +4668,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>-0.0164</v>
+        <v>0.955</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>965700</v>
+        <v>1302200</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="H94" t="n">
-        <v>53.74</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.16</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>3.597</v>
+        <v>0.992</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2.783</v>
+        <v>1.065</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4713,39 +4713,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>-0.0157</v>
+        <v>12.98</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>793300</v>
+        <v>1252500</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="H95" t="n">
-        <v>46</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.82</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.637</v>
+        <v>13.023</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.612</v>
+        <v>13.544</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4758,28 +4758,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>-0.0073</v>
+        <v>-0.0229</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>783900</v>
+        <v>1243200</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.22</v>
+        <v>0.65</v>
       </c>
       <c r="H96" t="n">
-        <v>58.08</v>
+        <v>49.77</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.302</v>
+        <v>1.275</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1.203</v>
+        <v>1.318</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4803,39 +4803,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0.0105</v>
+        <v>1.76</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>767500</v>
+        <v>1202100</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H97" t="n">
-        <v>36.33</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.14</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.993</v>
+        <v>1.755</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.065</v>
+        <v>1.778</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4848,39 +4848,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.915</v>
+        <v>0.61</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>-0.0054</v>
+        <v>-0.0161</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>746900</v>
+        <v>1197300</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H98" t="n">
-        <v>48.15</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.13</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.912</v>
+        <v>0.615</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.963</v>
+        <v>0.608</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4893,39 +4893,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.09</v>
+        <v>0.265</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>-0.018</v>
+        <v>-0.0185</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>745900</v>
+        <v>1190100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="H99" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.04</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.06</v>
+        <v>0.252</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.902</v>
+        <v>0.221</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4938,28 +4938,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.315</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>743400</v>
+        <v>1183400</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="H100" t="n">
-        <v>57.22</v>
+        <v>40.08</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.801</v>
+        <v>0.329</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.703</v>
+        <v>0.33</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4983,28 +4983,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.535</v>
+        <v>0.295</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>-0.0273</v>
+        <v>-0.0328</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>724400</v>
+        <v>1181900</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.18</v>
+        <v>1.23</v>
       </c>
       <c r="H101" t="n">
-        <v>66.45999999999999</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.483</v>
+        <v>0.269</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.454</v>
+        <v>0.266</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5028,28 +5028,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>-0.008</v>
+        <v>0.345</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>716900</v>
+        <v>1152100</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.09</v>
+        <v>0.87</v>
       </c>
       <c r="H102" t="n">
-        <v>35.12</v>
+        <v>41.57</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.281</v>
+        <v>0.349</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1.379</v>
+        <v>0.382</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5073,28 +5073,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>-0.0239</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>707400</v>
+        <v>1148800</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H103" t="n">
-        <v>81.06999999999999</v>
+        <v>45.96</v>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.057</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.627</v>
+        <v>2.083</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5118,28 +5118,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>3.17</v>
+        <v>0.47</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>-0.0186</v>
+        <v>-0.0105</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>698200</v>
+        <v>1148500</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="H104" t="n">
-        <v>44.76</v>
+        <v>54.34</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>3.194</v>
+        <v>0.462</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>3.382</v>
+        <v>0.461</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5163,28 +5163,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.78</v>
+        <v>0.915</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>-0.0189</v>
+        <v>-0.0054</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>672400</v>
+        <v>1143700</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H105" t="n">
-        <v>46.17</v>
+        <v>56.51</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.791</v>
+        <v>0.908</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.806</v>
+        <v>0.865</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5208,39 +5208,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.275</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>637800</v>
+        <v>1142600</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="H106" t="n">
-        <v>65.52</v>
-      </c>
-      <c r="I106" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.85</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>3.995</v>
+        <v>0.288</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.468</v>
+        <v>0.307</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5253,28 +5253,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.795</v>
+        <v>0.455</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>636400</v>
+        <v>1124600</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="H107" t="n">
-        <v>64.38</v>
+        <v>60.72</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.741</v>
+        <v>0.429</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.657</v>
+        <v>0.414</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5298,39 +5298,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>631300</v>
+        <v>1120400</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="H108" t="n">
-        <v>57.32</v>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.8</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2.635</v>
+        <v>0.911</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.587</v>
+        <v>0.963</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5343,28 +5343,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.725</v>
+        <v>1.92</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0052</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>605800</v>
+        <v>1116900</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="H109" t="n">
-        <v>46.48</v>
+        <v>47.08</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.733</v>
+        <v>1.928</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.748</v>
+        <v>1.956</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5388,39 +5388,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E110" s="8" t="n">
-        <v>-0.0069</v>
+        <v>0.62</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>573100</v>
+        <v>1115000</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.09</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.752</v>
+        <v>0.613</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5433,28 +5433,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.59</v>
+        <v>1.28</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>-0.0167</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>567900</v>
+        <v>1054700</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H111" t="n">
-        <v>37.34</v>
+        <v>43.38</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.614</v>
+        <v>1.319</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.634</v>
+        <v>1.308</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5478,39 +5478,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RCECAP</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.02</v>
+        <v>0.555</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.0355</v>
+        <v>0.0183</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>567400</v>
+        <v>1047800</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H112" t="n">
-        <v>62.14</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.75</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.984</v>
+        <v>0.581</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1.014</v>
+        <v>0.621</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5523,39 +5523,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0.0068</v>
+        <v>1.09</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>562800</v>
+        <v>891300</v>
       </c>
       <c r="G113" s="5" t="n">
         <v>0.18</v>
       </c>
       <c r="H113" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.7</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.759</v>
+        <v>1.06</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.748</v>
+        <v>0.902</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5568,39 +5568,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.665</v>
+        <v>1.24</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>-0.0075</v>
+        <v>-0.008</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>543600</v>
+        <v>851700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H114" t="n">
-        <v>61.84</v>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.12</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.64</v>
+        <v>1.281</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.604</v>
+        <v>1.379</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5613,39 +5613,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>533800</v>
+        <v>848100</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H115" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>5.518</v>
+        <v>0.791</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>5.374</v>
+        <v>0.806</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5658,28 +5658,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.535</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>527300</v>
+        <v>847800</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="H116" t="n">
-        <v>42.86</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>13.022</v>
+        <v>0.483</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>13.544</v>
+        <v>0.454</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5703,39 +5703,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0.005600000000000001</v>
+        <v>1.36</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>516400</v>
+        <v>838700</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H117" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.08</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.953</v>
+        <v>1.302</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.99</v>
+        <v>1.203</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5748,45 +5748,1305 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>-0.012</v>
+        <v>6.16</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>510000</v>
+        <v>824500</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H118" t="n">
-        <v>70.45</v>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.37</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.758</v>
+        <v>6.444</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.668</v>
+        <v>6.818</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>824000</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H119" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>3.382</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>801100</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H120" t="n">
+        <v>46</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>800300</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H121" t="n">
+        <v>81.06999999999999</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>798800</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H122" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>2.703</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>776900</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H123" t="n">
+        <v>64.76000000000001</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>3.468</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>751100</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H124" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>729400</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H125" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>722900</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H126" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>2.636</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>2.588</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>706800</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H127" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H128" t="n">
+        <v>61.84</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>688500</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>5.515</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>5.373</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>685700</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H130" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>685100</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H131" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>2.093</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>2.041</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>683000</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H132" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>4.486</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>4.805</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>656100</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H133" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>2.786</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>644500</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H134" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>619100</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H135" t="n">
+        <v>72.91</v>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>7.315</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>6.791</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>RCECAP</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>617700</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H136" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>614600</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>568800</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H138" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>555800</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H139" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>2.074</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>553300</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H140" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>525100</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H141" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>1.877</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>521300</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H142" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>517200</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H143" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>515300</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H144" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>513500</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H145" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>1.921</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>508500</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H146" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M118"/>
+  <autoFilter ref="A1:M146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
+++ b/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-12" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>118532000</v>
+        <v>119829400</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H2" t="n">
         <v>23.54</v>
@@ -603,10 +603,10 @@
         <v>-0.058</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>91900600</v>
+        <v>100268300</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
         <v>68.2</v>
@@ -648,10 +648,10 @@
         <v>-0.0278</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>36664500</v>
+        <v>37262500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H4" t="n">
         <v>57.25</v>
@@ -693,10 +693,10 @@
         <v>-0.1649</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>28618500</v>
+        <v>31734100</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>7.39</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>23.29</v>
@@ -738,10 +738,10 @@
         <v>0.0095</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22065200</v>
+        <v>26143900</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="H6" t="n">
         <v>76.25</v>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.19</v>
+        <v>0.515</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.05</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15753400</v>
+        <v>16690000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H7" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.66</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.196</v>
+        <v>0.493</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.184</v>
+        <v>0.48</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.515</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15038300</v>
+        <v>16243800</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="H8" t="n">
-        <v>60.66</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.99</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.493</v>
+        <v>0.196</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.48</v>
+        <v>0.184</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,33 +858,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>13285200</v>
+        <v>14737200</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.38</v>
+        <v>2.48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>77.36</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+      <c r="J9" s="2" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.276</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
@@ -896,40 +903,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0181</v>
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13199500</v>
+        <v>14662300</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H10" t="n">
-        <v>66.93000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>2.644</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>2.51</v>
-      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
@@ -941,28 +941,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.05</v>
+        <v>0.82</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.0296</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13024900</v>
+        <v>14025800</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2.19</v>
+        <v>0.19</v>
       </c>
       <c r="H11" t="n">
-        <v>73.67</v>
+        <v>58.51</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.292</v>
+        <v>0.786</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.276</v>
+        <v>0.713</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,28 +986,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>12955900</v>
+        <v>13817500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="H12" t="n">
-        <v>71.59999999999999</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.586</v>
+        <v>2.644</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.51</v>
+        <v>2.51</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,28 +1031,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>-0.0237</v>
+        <v>0.625</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11616000</v>
+        <v>13141000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>59.46</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.786</v>
+        <v>0.586</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.713</v>
+        <v>0.51</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1091,10 +1091,10 @@
         <v>-0.007900000000000001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10616200</v>
+        <v>10876000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
         <v>61.61</v>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>-0.0345</v>
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7181300</v>
+        <v>9765500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.3</v>
+        <v>1.48</v>
       </c>
       <c r="H15" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.8</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.411</v>
+        <v>0.115</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.35</v>
+        <v>0.122</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.046</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7034900</v>
+        <v>8698300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="H16" t="n">
-        <v>70.36</v>
+        <v>54.57</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.361</v>
+        <v>0.41</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.243</v>
+        <v>0.35</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LUSTER</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.025</v>
+        <v>0.39</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6875500</v>
+        <v>8391900</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.27</v>
+        <v>0.23</v>
       </c>
       <c r="H17" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.36</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.026</v>
+        <v>0.361</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.028</v>
+        <v>0.243</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>-0.0421</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6431500</v>
+        <v>7630200</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="H18" t="n">
-        <v>24.62</v>
+        <v>61.5</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.54</v>
+        <v>0.516</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.737</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.0215</v>
+        <v>0.455</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-0.0421</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6114900</v>
+        <v>7570700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="H19" t="n">
-        <v>79.70999999999999</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.62</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.369</v>
+        <v>0.54</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.352</v>
+        <v>0.737</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,28 +1346,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>LUSTER</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.025</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5761000</v>
+        <v>6935400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="H20" t="n">
-        <v>26.57</v>
+        <v>41.7</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.584</v>
+        <v>0.026</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.638</v>
+        <v>0.028</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.39</v>
+        <v>0.505</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>-0.06709999999999999</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5567100</v>
+        <v>6888300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3.16</v>
+        <v>1.24</v>
       </c>
       <c r="H21" t="n">
-        <v>27.73</v>
+        <v>25.92</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.497</v>
+        <v>0.584</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1.613</v>
+        <v>0.638</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,36 +1436,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>0.805</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5425000</v>
+        <v>6853700</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
+        <v>58.16</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.716</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1477,28 +1481,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.013</v>
+        <v>0.82</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5380300</v>
+        <v>6691300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H23" t="n">
-        <v>53.34</v>
+        <v>58.27</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1506,10 +1510,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.775</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.775</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1522,28 +1526,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5215000</v>
+        <v>6556000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.63</v>
+        <v>0.35</v>
       </c>
       <c r="H24" t="n">
-        <v>52.49</v>
+        <v>55.85</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1551,10 +1555,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.154</v>
+        <v>0.306</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.152</v>
+        <v>0.296</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1567,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.013</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5127400</v>
+        <v>6504700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="H25" t="n">
-        <v>57.36</v>
+        <v>53.34</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -1596,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.28</v>
+        <v>0.775</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.303</v>
+        <v>0.775</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1612,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>-0.2</v>
+        <v>0.48</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5022000</v>
+        <v>6429900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.27</v>
+        <v>1.89</v>
       </c>
       <c r="H26" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.19</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.024</v>
+        <v>0.37</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.024</v>
+        <v>0.352</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1657,39 +1661,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>1.38</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>-0.0738</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4919200</v>
+        <v>6330700</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.31</v>
+        <v>3.59</v>
       </c>
       <c r="H27" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.89</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.496</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.613</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1702,40 +1706,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4714000</v>
+        <v>5440900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="H28" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>0.716</v>
-      </c>
+        <v>41.68</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1747,28 +1747,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>-0.026</v>
+        <v>0.155</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4450600</v>
+        <v>5215000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.53</v>
+        <v>2.63</v>
       </c>
       <c r="H29" t="n">
-        <v>63.01</v>
+        <v>52.49</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.356</v>
+        <v>0.154</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.323</v>
+        <v>0.152</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1792,28 +1792,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>-0.0159</v>
+        <v>0.295</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4366000</v>
+        <v>5188100</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="H30" t="n">
-        <v>55.85</v>
+        <v>57.36</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.306</v>
+        <v>0.28</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.296</v>
+        <v>0.303</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1837,39 +1837,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.22</v>
+        <v>0.37</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.0278</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4240800</v>
+        <v>5076600</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="H31" t="n">
-        <v>43.61</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.83</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.225</v>
+        <v>0.347</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.241</v>
+        <v>0.326</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1882,39 +1882,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.62</v>
+        <v>0.02</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.2</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4240600</v>
+        <v>5022000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="H32" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.3</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.613</v>
+        <v>0.024</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.612</v>
+        <v>0.024</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1927,28 +1927,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>-0.0185</v>
+        <v>0.225</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3900000</v>
+        <v>4976300</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H33" t="n">
-        <v>40.24</v>
+        <v>47.33</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.216</v>
+        <v>0.225</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2.217</v>
+        <v>0.241</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1972,39 +1972,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0.0286</v>
+        <v>0.375</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>-0.026</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3898400</v>
+        <v>4976300</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="H34" t="n">
-        <v>58.49</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.01</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.514</v>
+        <v>0.356</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.441</v>
+        <v>0.323</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2017,28 +2017,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.62</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3884300</v>
+        <v>4681300</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="H35" t="n">
-        <v>56.18</v>
+        <v>54.39</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.105</v>
+        <v>0.613</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2.085</v>
+        <v>0.612</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2062,39 +2062,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>-0.0203</v>
+        <v>0.175</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3810600</v>
+        <v>4522100</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="H36" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.44</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.696</v>
+        <v>0.184</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.681</v>
+        <v>0.197</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2107,39 +2107,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.22</v>
+        <v>4.66</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.0197</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3551100</v>
+        <v>4503800</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>3.89</v>
+        <v>0.28</v>
       </c>
       <c r="H37" t="n">
-        <v>75.02</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.05</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.208</v>
+        <v>4.716</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.205</v>
+        <v>4.884</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2152,39 +2152,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0139</v>
+        <v>2.12</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3546200</v>
+        <v>4375400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>62.19</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.24</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.346</v>
+        <v>2.216</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.326</v>
+        <v>2.217</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2197,39 +2197,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0175</v>
+        <v>0.865</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3500400</v>
+        <v>4363200</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H39" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.92</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.715</v>
+        <v>0.868</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.883</v>
+        <v>0.869</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2242,39 +2242,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.22</v>
+        <v>0.725</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>-0.0222</v>
+        <v>-0.0203</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3465500</v>
+        <v>4057600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="H40" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.3</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.246</v>
+        <v>0.696</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.301</v>
+        <v>0.681</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2287,28 +2287,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>-0.0159</v>
+        <v>2.15</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3251000</v>
+        <v>4027000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>11.87</v>
+        <v>0.21</v>
       </c>
       <c r="H41" t="n">
-        <v>59.79</v>
+        <v>57.43</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.294</v>
+        <v>2.106</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.297</v>
+        <v>2.086</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2332,28 +2332,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3228800</v>
+        <v>3861900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="H42" t="n">
-        <v>55.22</v>
+        <v>59.69</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.122</v>
+        <v>0.675</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.125</v>
+        <v>0.611</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2377,39 +2377,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.7</v>
+        <v>0.49</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-0.0278</v>
+        <v>-0.02</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3182400</v>
+        <v>3837800</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="H43" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.76</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.675</v>
+        <v>0.521</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.611</v>
+        <v>0.569</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2422,39 +2422,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0038</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ARTRONIQ</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.225</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3144500</v>
+        <v>3712400</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>9.66</v>
+        <v>0.14</v>
       </c>
       <c r="H44" t="n">
-        <v>79.14</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.08</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.134</v>
+        <v>0.247</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.132</v>
+        <v>0.301</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2467,39 +2467,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UOADEV</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.51</v>
+        <v>0.22</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0233</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3078000</v>
+        <v>3623700</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>14.54</v>
+        <v>3.97</v>
       </c>
       <c r="H45" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.02</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.558</v>
+        <v>0.208</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.614</v>
+        <v>0.205</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2512,39 +2512,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.17</v>
+        <v>0.125</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3053100</v>
+        <v>3517600</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H46" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.22</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.184</v>
+        <v>0.122</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.197</v>
+        <v>0.125</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2557,39 +2557,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0038</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>ARTRONIQ</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.725</v>
+        <v>0.145</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0357</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3016800</v>
+        <v>3479600</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.61</v>
+        <v>10.69</v>
       </c>
       <c r="H47" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.14</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.733</v>
+        <v>0.134</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.748</v>
+        <v>0.132</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2602,39 +2602,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>-0.0125</v>
+        <v>7.31</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2937700</v>
+        <v>3449500</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="H48" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.47</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.781</v>
+        <v>7.609</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.773</v>
+        <v>7.723</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2647,28 +2647,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.265</v>
+        <v>0.31</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>-0.0364</v>
+        <v>-0.0159</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2881800</v>
+        <v>3291000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1.3</v>
+        <v>12.01</v>
       </c>
       <c r="H49" t="n">
-        <v>55.66</v>
+        <v>59.79</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.252</v>
+        <v>0.294</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.254</v>
+        <v>0.297</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2692,28 +2692,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2554700</v>
+        <v>3264400</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1.23</v>
+        <v>0.6</v>
       </c>
       <c r="H50" t="n">
-        <v>80.15000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.211</v>
+        <v>0.165</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.174</v>
+        <v>0.166</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2737,28 +2737,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.2</v>
+        <v>0.79</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>-0.0323</v>
+        <v>-0.0125</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2549300</v>
+        <v>3257100</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="H51" t="n">
-        <v>55.23</v>
+        <v>53.58</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.163</v>
+        <v>0.781</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.17</v>
+        <v>0.773</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2782,39 +2782,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5</v>
+        <v>0.32</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>-0.0177</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2522300</v>
+        <v>3230100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="H52" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.76</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.932</v>
+        <v>0.326</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4.669</v>
+        <v>0.339</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2827,28 +2827,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>-0.0259</v>
+        <v>0.725</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.014</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2483800</v>
+        <v>3189900</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.31</v>
+        <v>1.7</v>
       </c>
       <c r="H53" t="n">
-        <v>51.21</v>
+        <v>46.48</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.959</v>
+        <v>0.733</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.826</v>
+        <v>0.748</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2872,28 +2872,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>UOADEV</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>7.3</v>
+        <v>1.51</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0067</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2460000</v>
+        <v>3078000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.18</v>
+        <v>14.54</v>
       </c>
       <c r="H54" t="n">
-        <v>33.89</v>
+        <v>27.9</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.608</v>
+        <v>1.558</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>7.723</v>
+        <v>1.614</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2917,39 +2917,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.32</v>
+        <v>0.265</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0364</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2448000</v>
+        <v>2981300</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.41</v>
+        <v>1.34</v>
       </c>
       <c r="H55" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.66</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.326</v>
+        <v>0.252</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.339</v>
+        <v>0.254</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2962,39 +2962,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.93</v>
+        <v>1.21</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>-0.0068</v>
+        <v>-0.032</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2410600</v>
+        <v>2933800</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.74</v>
+        <v>0.36</v>
       </c>
       <c r="H56" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.96</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.674</v>
+        <v>1.278</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.309</v>
+        <v>1.379</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3007,39 +3007,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.2</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2366100</v>
+        <v>2871100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.8</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.868</v>
+        <v>0.206</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.869</v>
+        <v>0.208</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3052,39 +3052,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.04</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>-0.028</v>
+        <v>-0.0311</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2360900</v>
+        <v>2807800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H58" t="n">
-        <v>45.74</v>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.47</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.069</v>
+        <v>0.959</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.038</v>
+        <v>0.826</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3097,39 +3097,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.495</v>
+        <v>1.04</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>-0.01</v>
+        <v>-0.028</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2357100</v>
+        <v>2743500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H59" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.74</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.522</v>
+        <v>1.069</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.57</v>
+        <v>1.038</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3142,39 +3142,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.53</v>
+        <v>5</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>-0.0185</v>
+        <v>-0.0177</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2348000</v>
+        <v>2718400</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="H60" t="n">
-        <v>52.71</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.523</v>
+        <v>4.932</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.531</v>
+        <v>4.669</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3187,28 +3187,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.705</v>
+        <v>1.2</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-0.0342</v>
+        <v>-0.0323</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2343200</v>
+        <v>2711000</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0.46</v>
       </c>
       <c r="H61" t="n">
-        <v>80.78</v>
+        <v>55.23</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.539</v>
+        <v>1.163</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.45</v>
+        <v>1.17</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3232,28 +3232,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.25</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2317200</v>
+        <v>2679500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="H62" t="n">
-        <v>63.6</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.776</v>
+        <v>0.211</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.763</v>
+        <v>0.174</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3277,28 +3277,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.87</v>
+        <v>0.705</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.0387</v>
+        <v>-0.0342</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2161400</v>
+        <v>2658900</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="H63" t="n">
-        <v>60.83</v>
+        <v>80.78</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.83</v>
+        <v>0.539</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.762</v>
+        <v>0.45</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3322,28 +3322,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>-0.0175</v>
+        <v>0.82</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0186</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2076100</v>
+        <v>2566900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.22</v>
+        <v>1.26</v>
       </c>
       <c r="H64" t="n">
-        <v>62.8</v>
+        <v>62.72</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.076</v>
+        <v>0.775</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.926</v>
+        <v>0.763</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3367,39 +3367,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0</v>
+        <v>2.92</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2023200</v>
+        <v>2527300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="H65" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.2</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.206</v>
+        <v>2.673</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.208</v>
+        <v>2.309</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3412,28 +3412,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.37</v>
+        <v>7.19</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>-0.0133</v>
+        <v>-0.0042</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2019800</v>
+        <v>2507000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H66" t="n">
-        <v>52.46</v>
+        <v>24.08</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.368</v>
+        <v>7.566</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.368</v>
+        <v>8.069000000000001</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3457,39 +3457,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.0074</v>
+        <v>0.53</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1969400</v>
+        <v>2378400</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H67" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.71</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>5.934</v>
+        <v>0.523</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>5.808</v>
+        <v>0.531</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3502,28 +3502,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>7.2</v>
+        <v>0.37</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>-0.0028</v>
+        <v>-0.0133</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1894600</v>
+        <v>2319800</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H68" t="n">
-        <v>24.32</v>
+        <v>52.46</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7.567</v>
+        <v>0.368</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>8.069000000000001</v>
+        <v>0.368</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3547,28 +3547,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.875</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0331</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1865600</v>
+        <v>2317100</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="H69" t="n">
-        <v>64.31999999999999</v>
+        <v>61.96</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.719</v>
+        <v>0.831</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.695</v>
+        <v>0.763</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3592,39 +3592,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1842500</v>
+        <v>2235400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H70" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.161</v>
+        <v>1.077</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1.122</v>
+        <v>0.926</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3637,39 +3637,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>-0.0318</v>
+        <v>12.96</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1747400</v>
+        <v>2208700</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3.55</v>
+        <v>0.24</v>
       </c>
       <c r="H71" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.86</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.267</v>
+        <v>13.022</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2.221</v>
+        <v>13.544</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3682,28 +3682,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>-0.0246</v>
+        <v>6.87</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1744200</v>
+        <v>2120700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="H72" t="n">
-        <v>70.64</v>
+        <v>67.25</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.038</v>
+        <v>5.937</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.871</v>
+        <v>5.809</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3727,39 +3727,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.52</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1719900</v>
+        <v>2094100</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H73" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.06</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.421</v>
+        <v>0.494</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.44</v>
+        <v>0.481</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3772,39 +3772,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.52</v>
+        <v>1.13</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.0189</v>
+        <v>-0.0174</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1687200</v>
+        <v>2081200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.85</v>
+        <v>0.21</v>
       </c>
       <c r="H74" t="n">
-        <v>62.06</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.97</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.494</v>
+        <v>1.16</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.481</v>
+        <v>1.121</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3817,39 +3817,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0</v>
+        <v>9.94</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1678700</v>
+        <v>2056300</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="H75" t="n">
-        <v>86.70999999999999</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.19</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>10.014</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.494</v>
+        <v>10.201</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3862,28 +3862,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>-0.0227</v>
+        <v>0.775</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1671600</v>
+        <v>1950600</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H76" t="n">
-        <v>54.98</v>
+        <v>63.64</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.211</v>
+        <v>0.718</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.19</v>
+        <v>0.695</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>-0.0123</v>
+        <v>1.65</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1648400</v>
+        <v>1933600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H77" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.76</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>5.644</v>
+        <v>1.668</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>5.338</v>
+        <v>1.78</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3952,39 +3952,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1617800</v>
+        <v>1898600</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.27</v>
+        <v>1.24</v>
       </c>
       <c r="H78" t="n">
-        <v>72.19</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.788</v>
+        <v>0.421</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.766</v>
+        <v>0.44</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3997,39 +3997,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.0488</v>
+        <v>5.65</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1607700</v>
+        <v>1895000</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1.57</v>
+        <v>0.14</v>
       </c>
       <c r="H79" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.5</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.204</v>
+        <v>5.646</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.211</v>
+        <v>5.338</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4042,28 +4042,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.295</v>
+        <v>0.6</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-0.0167</v>
+        <v>-0.0083</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1597000</v>
+        <v>1841100</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="H80" t="n">
-        <v>52.19</v>
+        <v>68.39</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.292</v>
+        <v>0.554</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.281</v>
+        <v>0.498</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4087,28 +4087,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0.0133</v>
+        <v>2.12</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1595000</v>
+        <v>1825500</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.12</v>
+        <v>3.71</v>
       </c>
       <c r="H81" t="n">
-        <v>42.19</v>
+        <v>36.94</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>10.014</v>
+        <v>2.266</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>10.201</v>
+        <v>2.221</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4132,28 +4132,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>-0.0083</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1532800</v>
+        <v>1815800</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H82" t="n">
-        <v>68.39</v>
+        <v>72.19</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
@@ -4161,10 +4161,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.554</v>
+        <v>0.788</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.498</v>
+        <v>0.766</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4177,39 +4177,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1507800</v>
+        <v>1805200</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1.23</v>
+        <v>0.49</v>
       </c>
       <c r="H83" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.08</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.385</v>
+        <v>1.039</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.395</v>
+        <v>0.871</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4222,28 +4222,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>-0.0241</v>
+        <v>0.22</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1488600</v>
+        <v>1732100</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.12</v>
+        <v>1.03</v>
       </c>
       <c r="H84" t="n">
-        <v>56.87</v>
+        <v>58.47</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.388</v>
+        <v>0.212</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.376</v>
+        <v>0.19</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4267,28 +4267,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>-0.0326</v>
+        <v>1.01</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1429100</v>
+        <v>1700200</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="H85" t="n">
-        <v>49.65</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.451</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.428</v>
+        <v>0.494</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4312,36 +4312,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.34</v>
+        <v>1.2</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>-0.0286</v>
+        <v>-0.0083</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1414500</v>
+        <v>1695900</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="H86" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="n"/>
+        <v>32.6</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1.31</v>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
     </row>
@@ -4353,39 +4357,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>-0.0083</v>
+        <v>0.215</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1411800</v>
+        <v>1654900</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.63</v>
+        <v>1.61</v>
       </c>
       <c r="H87" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.54000000000001</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.281</v>
+        <v>0.204</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.31</v>
+        <v>0.211</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4398,28 +4402,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.22</v>
+        <v>0.78</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0189</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1406300</v>
+        <v>1613900</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1.81</v>
+        <v>0.39</v>
       </c>
       <c r="H88" t="n">
-        <v>40.88</v>
+        <v>46.17</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4427,10 +4431,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.231</v>
+        <v>0.791</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.234</v>
+        <v>0.806</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4443,39 +4447,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0435</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1372300</v>
+        <v>1613200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.35</v>
+        <v>2.07</v>
       </c>
       <c r="H89" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.88</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.601</v>
+        <v>0.231</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.583</v>
+        <v>0.234</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4488,39 +4492,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0.0154</v>
+        <v>0.295</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1367900</v>
+        <v>1607200</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H90" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.19</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.338</v>
+        <v>0.292</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.344</v>
+        <v>0.281</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4533,28 +4537,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1.65</v>
+        <v>0.96</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0.0185</v>
+        <v>0.0052</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1348500</v>
+        <v>1603900</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="H91" t="n">
-        <v>43.76</v>
+        <v>34.31</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4562,10 +4566,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.668</v>
+        <v>0.993</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.78</v>
+        <v>1.065</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4578,28 +4582,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>-0.0208</v>
+        <v>0.38</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1341900</v>
+        <v>1590500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.43</v>
+        <v>1.3</v>
       </c>
       <c r="H92" t="n">
-        <v>46.24</v>
+        <v>38.45</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4607,10 +4611,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.241</v>
+        <v>0.385</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.249</v>
+        <v>0.395</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4623,39 +4627,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>3.57</v>
+        <v>0.64</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>-0.0246</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1320800</v>
+        <v>1585300</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="H93" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.7</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>3.594</v>
+        <v>0.601</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2.782</v>
+        <v>0.583</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4668,28 +4672,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1302200</v>
+        <v>1570200</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="H94" t="n">
-        <v>32.16</v>
+        <v>56.87</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4697,10 +4701,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.992</v>
+        <v>0.388</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.065</v>
+        <v>0.376</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4713,39 +4717,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.34</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1252500</v>
+        <v>1551600</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.14</v>
+        <v>1.17</v>
       </c>
       <c r="H95" t="n">
-        <v>43.82</v>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.96</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>13.023</v>
+        <v>0.348</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>13.544</v>
+        <v>0.381</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4758,40 +4762,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.28</v>
+        <v>0.34</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>-0.0229</v>
+        <v>-0.0286</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1243200</v>
+        <v>1495300</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="H96" t="n">
-        <v>49.77</v>
+        <v>66.19</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J96" s="2" t="n">
-        <v>1.275</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>1.318</v>
-      </c>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="n"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
     </row>
@@ -4803,28 +4803,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.76</v>
+        <v>0.235</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>-0.0112</v>
+        <v>-0.0208</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1202100</v>
+        <v>1491900</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="H97" t="n">
-        <v>50.14</v>
+        <v>46.24</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.755</v>
+        <v>0.241</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.778</v>
+        <v>0.249</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4848,28 +4848,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>-0.0161</v>
+        <v>-0.0217</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1197300</v>
+        <v>1479300</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="H98" t="n">
-        <v>49.13</v>
+        <v>50.84</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.615</v>
+        <v>0.451</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.608</v>
+        <v>0.428</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4893,28 +4893,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E99" s="8" t="n">
-        <v>-0.0185</v>
+        <v>6.18</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1190100</v>
+        <v>1473900</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H99" t="n">
-        <v>61.04</v>
+        <v>29.97</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.252</v>
+        <v>6.446</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.221</v>
+        <v>6.818</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4938,28 +4938,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1183400</v>
+        <v>1442900</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="H100" t="n">
-        <v>40.08</v>
+        <v>30.92</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.329</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.33</v>
+        <v>0.582</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4983,39 +4983,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.295</v>
+        <v>0.905</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0163</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1181900</v>
+        <v>1417600</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.23</v>
+        <v>0.27</v>
       </c>
       <c r="H101" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.28</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.269</v>
+        <v>0.907</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.266</v>
+        <v>0.864</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5028,28 +5028,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>0</v>
+        <v>3.57</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>-0.0246</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1152100</v>
+        <v>1382400</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.87</v>
+        <v>0.13</v>
       </c>
       <c r="H102" t="n">
-        <v>41.57</v>
+        <v>52.99</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.349</v>
+        <v>3.594</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.382</v>
+        <v>2.782</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5073,39 +5073,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E103" s="8" t="n">
-        <v>-0.0239</v>
+        <v>0.325</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1148800</v>
+        <v>1369200</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="H103" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.39</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.057</v>
+        <v>0.338</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2.083</v>
+        <v>0.344</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5118,28 +5118,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.47</v>
+        <v>2.04</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>-0.0105</v>
+        <v>-0.0239</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1148500</v>
+        <v>1330800</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="H104" t="n">
-        <v>54.34</v>
+        <v>45.96</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.462</v>
+        <v>2.057</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.461</v>
+        <v>2.083</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5163,39 +5163,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E105" s="8" t="n">
-        <v>-0.0054</v>
+        <v>0.62</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1143700</v>
+        <v>1329500</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="H105" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.908</v>
+        <v>0.613</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.865</v>
+        <v>0.599</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5208,28 +5208,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.275</v>
+        <v>0.26</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>-0.0179</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1142600</v>
+        <v>1291900</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H106" t="n">
-        <v>33.85</v>
+        <v>58.06</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.288</v>
+        <v>0.252</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.307</v>
+        <v>0.221</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5253,39 +5253,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>1.77</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1124600</v>
+        <v>1289300</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H107" t="n">
-        <v>60.72</v>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.429</v>
+        <v>1.756</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.414</v>
+        <v>1.778</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5298,39 +5298,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.905</v>
+        <v>0.45</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>-0.0163</v>
+        <v>-0.011</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1120400</v>
+        <v>1288600</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="H108" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.92</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.911</v>
+        <v>0.428</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.963</v>
+        <v>0.414</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5343,39 +5343,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0.0052</v>
+        <v>1.28</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1116900</v>
+        <v>1288300</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="H109" t="n">
-        <v>47.08</v>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.77</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.928</v>
+        <v>1.275</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.956</v>
+        <v>1.318</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5388,28 +5388,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>-0.0242</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1115000</v>
+        <v>1286900</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H110" t="n">
-        <v>64.43000000000001</v>
+        <v>47.97</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.613</v>
+        <v>0.614</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.599</v>
+        <v>0.608</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5433,28 +5433,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.28</v>
+        <v>2.84</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0035</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1054700</v>
+        <v>1260800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H111" t="n">
-        <v>43.38</v>
+        <v>55.57</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.319</v>
+        <v>2.8</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1.308</v>
+        <v>2.703</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5478,39 +5478,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.295</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1047800</v>
+        <v>1203500</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="H112" t="n">
-        <v>37.75</v>
-      </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.581</v>
+        <v>0.269</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.621</v>
+        <v>0.266</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5523,39 +5523,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>-0.018</v>
+        <v>0.315</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>891300</v>
+        <v>1193400</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.18</v>
+        <v>0.61</v>
       </c>
       <c r="H113" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.08</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.06</v>
+        <v>0.329</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.902</v>
+        <v>0.33</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5568,39 +5568,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>-0.008</v>
+        <v>-0.0248</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>851700</v>
+        <v>1190700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H114" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.34</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.281</v>
+        <v>3.192</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1.379</v>
+        <v>3.381</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5613,28 +5613,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.785</v>
+        <v>0.275</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>-0.0126</v>
+        <v>-0.0179</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>848100</v>
+        <v>1158500</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="H115" t="n">
-        <v>47.41</v>
+        <v>33.85</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.791</v>
+        <v>0.288</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.806</v>
+        <v>0.307</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5658,39 +5658,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E116" s="8" t="n">
-        <v>-0.0273</v>
+        <v>4.49</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.0205</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>847800</v>
+        <v>1157900</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H116" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.76</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.483</v>
+        <v>4.486</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.454</v>
+        <v>4.805</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5703,28 +5703,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.36</v>
+        <v>0.785</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>-0.0073</v>
+        <v>-0.0126</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>838700</v>
+        <v>1151000</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="H117" t="n">
-        <v>58.08</v>
+        <v>62.14</v>
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.302</v>
+        <v>0.74</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.203</v>
+        <v>0.657</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5748,39 +5748,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0.0098</v>
+        <v>0.47</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>824500</v>
+        <v>1148800</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.17</v>
+        <v>0.61</v>
       </c>
       <c r="H118" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.34</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>6.444</v>
+        <v>0.462</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>6.818</v>
+        <v>0.461</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5793,39 +5793,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>3.17</v>
+        <v>1.27</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>-0.0186</v>
+        <v>-0.0155</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>824000</v>
+        <v>1147700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H119" t="n">
-        <v>44.76</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.08</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>3.194</v>
+        <v>1.318</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>3.382</v>
+        <v>1.307</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5838,28 +5838,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.625</v>
+        <v>0.905</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>-0.0157</v>
+        <v>-0.0163</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>801100</v>
+        <v>1137300</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="H120" t="n">
-        <v>46</v>
+        <v>44.8</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.637</v>
+        <v>0.911</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.612</v>
+        <v>0.963</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5883,39 +5883,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>1.92</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>800300</v>
+        <v>1117400</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H121" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.08</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.928</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.627</v>
+        <v>1.956</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5928,39 +5928,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>0</v>
+        <v>1.09</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>798800</v>
+        <v>1074200</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="H122" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.7</v>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2.8</v>
+        <v>1.06</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.703</v>
+        <v>0.902</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5973,39 +5973,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>4.25</v>
+        <v>0.555</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.0183</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>776900</v>
+        <v>1047800</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H123" t="n">
-        <v>64.76000000000001</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.75</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>3.992</v>
+        <v>0.581</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>3.468</v>
+        <v>0.621</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6018,39 +6018,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.79</v>
+        <v>0.865</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>-0.0063</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>751100</v>
+        <v>1040000</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="H124" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.91</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.74</v>
+        <v>0.865</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.657</v>
+        <v>0.859</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6063,28 +6063,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.82</v>
+        <v>0.455</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>-0.018</v>
+        <v>-0.0319</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>729400</v>
+        <v>1028600</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="H125" t="n">
-        <v>68.98999999999999</v>
+        <v>53.37</v>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.757</v>
+        <v>0.447</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.668</v>
+        <v>0.451</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6108,39 +6108,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>0.0037</v>
+        <v>2.44</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>722900</v>
+        <v>1009800</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="H126" t="n">
-        <v>58.03</v>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.61</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>2.636</v>
+        <v>2.596</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2.588</v>
+        <v>2.776</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6153,28 +6153,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.59</v>
+        <v>1.72</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>-0.0167</v>
+        <v>-0.0282</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>706800</v>
+        <v>959100</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>37.34</v>
+        <v>35.67</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.614</v>
+        <v>1.814</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.634</v>
+        <v>1.921</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6198,28 +6198,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.665</v>
+        <v>0.8</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>-0.0075</v>
+        <v>-0.0062</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>700000</v>
+        <v>959000</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="H128" t="n">
-        <v>61.84</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.64</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.604</v>
+        <v>0.627</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6243,28 +6243,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>5.87</v>
+        <v>0.82</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>-0.0051</v>
+        <v>-0.018</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>688500</v>
+        <v>950300</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H129" t="n">
-        <v>62.08</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>5.515</v>
+        <v>0.757</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>5.373</v>
+        <v>0.668</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6288,39 +6288,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>685700</v>
+        <v>904000</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H130" t="n">
-        <v>25.54</v>
-      </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.99</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.952</v>
+        <v>0.641</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.99</v>
+        <v>0.604</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6333,28 +6333,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.13</v>
+        <v>4.26</v>
       </c>
       <c r="E131" s="10" t="n">
         <v>0.004699999999999999</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>685100</v>
+        <v>897900</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="H131" t="n">
-        <v>55.69</v>
+        <v>65.02</v>
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>2.093</v>
+        <v>3.993</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>2.041</v>
+        <v>3.468</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6378,39 +6378,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4.49</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>0.0205</v>
+        <v>0.0089</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>683000</v>
+        <v>875600</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.13</v>
+        <v>0.41</v>
       </c>
       <c r="H132" t="n">
-        <v>45.76</v>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.15</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>4.486</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>4.805</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6423,28 +6423,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>0</v>
+        <v>1.35</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>656100</v>
+        <v>870100</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H133" t="n">
-        <v>57.64</v>
+        <v>57.04</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
@@ -6452,10 +6452,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.786</v>
+        <v>1.301</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.612</v>
+        <v>1.202</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6468,28 +6468,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1.23</v>
+        <v>0.54</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>-0.0315</v>
+        <v>-0.0182</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>644500</v>
+        <v>869400</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H134" t="n">
-        <v>65.12</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.099</v>
+        <v>0.483</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.842</v>
+        <v>0.454</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6528,10 +6528,10 @@
         <v>0.0038</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>619100</v>
+        <v>859200</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="H135" t="n">
         <v>72.91</v>
@@ -6558,28 +6558,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>RCECAP</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.01</v>
+        <v>2.71</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>0.0254</v>
+        <v>0.0037</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>617700</v>
+        <v>836300</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>1.09</v>
+        <v>0.14</v>
       </c>
       <c r="H136" t="n">
-        <v>59.17</v>
+        <v>58.03</v>
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.983</v>
+        <v>2.636</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1.014</v>
+        <v>2.588</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6603,39 +6603,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>0</v>
+        <v>5.89</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>614600</v>
+        <v>804600</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="H137" t="n">
-        <v>33.64</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.76</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.753</v>
+        <v>5.517</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>5.374</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6648,28 +6648,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>568800</v>
+        <v>801600</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="H138" t="n">
-        <v>46.05</v>
+        <v>46</v>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.759</v>
+        <v>0.637</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.748</v>
+        <v>0.612</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6693,28 +6693,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>0</v>
+        <v>2.87</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>555800</v>
+        <v>768300</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H139" t="n">
-        <v>69.42</v>
+        <v>58.15</v>
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>2.727</v>
+        <v>2.787</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>2.074</v>
+        <v>2.612</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6738,28 +6738,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>RCECAP</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>0</v>
+        <v>1.01</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0.0254</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>553300</v>
+        <v>737900</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.09</v>
+        <v>1.3</v>
       </c>
       <c r="H140" t="n">
-        <v>50.56</v>
+        <v>59.17</v>
       </c>
       <c r="I140" s="9" t="inlineStr">
         <is>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>1.25</v>
+        <v>0.983</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1.284</v>
+        <v>1.014</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6783,39 +6783,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>525100</v>
+        <v>719000</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="H141" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.61</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>1.877</v>
+        <v>2.094</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.01</v>
+        <v>2.041</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6828,39 +6828,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.885</v>
+        <v>1.23</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>-0.0112</v>
+        <v>-0.0315</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>521300</v>
+        <v>715000</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
       <c r="H142" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.12</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.02</v>
+        <v>1.099</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1.113</v>
+        <v>0.842</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6873,28 +6873,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>0.0154</v>
+        <v>0.59</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>517200</v>
+        <v>707800</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H143" t="n">
-        <v>61.87</v>
+        <v>37.34</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6902,10 +6902,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.625</v>
+        <v>0.614</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.533</v>
+        <v>0.634</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6918,28 +6918,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.9</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>515300</v>
+        <v>705100</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="H144" t="n">
-        <v>72.79000000000001</v>
+        <v>25.54</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>1.25</v>
+        <v>0.952</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6963,28 +6963,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E145" s="8" t="n">
-        <v>-0.0226</v>
+        <v>0.655</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>513500</v>
+        <v>661900</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="H145" t="n">
-        <v>36.51</v>
+        <v>61.06</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.815</v>
+        <v>0.625</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1.921</v>
+        <v>0.533</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -7008,28 +7008,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E146" s="8" t="n">
-        <v>-0.0136</v>
+        <v>0.72</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>508500</v>
+        <v>657800</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H146" t="n">
-        <v>43.56</v>
+        <v>33.64</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7037,16 +7037,601 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>2.97</v>
+        <v>0.753</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>3.033</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>641100</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H147" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>628500</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H148" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>626600</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H149" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>617900</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H150" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>2.971</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>605900</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H151" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>586600</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H152" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>2.726</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>548500</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H153" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>529200</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H154" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>TEOSENG</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>-0.0296</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>526400</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H155" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>MISC</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>526200</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H156" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>7.742</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>7.897</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>518000</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H157" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>-0.0309</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>513100</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H158" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>502100</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H159" t="n">
+        <v>61.88</v>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>2.817</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M146"/>
+  <autoFilter ref="A1:M159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
+++ b/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-12" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
-    </font>
-    <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
+    </font>
+    <font>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,13 +78,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0.0588</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>119829400</v>
+        <v>126164100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H2" t="n">
-        <v>23.54</v>
+        <v>23.09</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>0.166</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -599,19 +599,19 @@
       <c r="D3" s="2" t="n">
         <v>0.325</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="3" t="n">
         <v>-0.058</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>100268300</v>
+        <v>104392800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
         <v>68.2</v>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>-0.0278</v>
+        <v>0.18</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>37262500</v>
+        <v>37909100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H4" t="n">
-        <v>57.25</v>
+        <v>60.1</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.1649</v>
+        <v>1.56</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.1702</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>31734100</v>
+        <v>37342400</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="H5" t="n">
-        <v>23.29</v>
+        <v>22.94</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.868</v>
+        <v>1.867</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>2.015</v>
@@ -738,15 +738,15 @@
         <v>0.0095</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>26143900</v>
+        <v>28068200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H6" t="n">
         <v>76.25</v>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -779,11 +779,11 @@
       <c r="D7" s="2" t="n">
         <v>0.515</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="3" t="n">
         <v>-0.009599999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>16690000</v>
+        <v>16747000</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.52</v>
@@ -791,7 +791,7 @@
       <c r="H7" t="n">
         <v>60.66</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -824,14 +824,14 @@
       <c r="D8" s="2" t="n">
         <v>0.19</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>16243800</v>
+        <v>16335600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H8" t="n">
         <v>47.99</v>
@@ -867,21 +867,21 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.0667</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14737200</v>
+        <v>15400100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>77.36</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -914,16 +914,16 @@
       <c r="D10" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14662300</v>
+        <v>15112800</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+        <v>0.43</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -952,19 +952,19 @@
       <c r="D11" s="2" t="n">
         <v>0.82</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="3" t="n">
         <v>-0.0296</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>14025800</v>
+        <v>14583200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="n">
         <v>58.51</v>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1001,15 +1001,15 @@
         <v>0.0181</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>13817500</v>
+        <v>14531300</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H12" t="n">
         <v>66.93000000000001</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1042,11 +1042,11 @@
       <c r="D13" s="2" t="n">
         <v>0.625</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>13141000</v>
+        <v>13141100</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.5</v>
@@ -1054,7 +1054,7 @@
       <c r="H13" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.11</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10876000</v>
+        <v>12475100</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.6</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>61.61</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.8</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.585</v>
+        <v>0.115</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.523</v>
+        <v>0.122</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E15" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>9765500</v>
+        <v>12466600</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.48</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.82</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.115</v>
+        <v>0.585</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.122</v>
+        <v>0.524</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>-0.046</v>
+        <v>0.155</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8698300</v>
+        <v>10758000</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H16" t="n">
-        <v>54.57</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
+        <v>46.1</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.41</v>
+        <v>0.156</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.35</v>
+        <v>0.157</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0.0345</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8391900</v>
+        <v>9547400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+        <v>56.03</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.361</v>
+        <v>0.411</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.243</v>
+        <v>0.35</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         <v>0.0667</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7630200</v>
+        <v>9522200</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="H18" t="n">
         <v>61.5</v>
@@ -1312,14 +1312,14 @@
       <c r="D19" s="2" t="n">
         <v>0.455</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="3" t="n">
         <v>-0.0421</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7570700</v>
+        <v>9393000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H19" t="n">
         <v>24.62</v>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LUSTER</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.025</v>
+        <v>0.8</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>-0.0123</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6935400</v>
+        <v>9215100</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.28</v>
+        <v>0.67</v>
       </c>
       <c r="H20" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.24</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.026</v>
+        <v>0.772</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.028</v>
+        <v>0.716</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,39 +1391,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>-0.07339999999999999</v>
+        <v>0.31</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6888300</v>
+        <v>8681000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.24</v>
+        <v>0.46</v>
       </c>
       <c r="H21" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.85</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.584</v>
+        <v>0.306</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.638</v>
+        <v>0.296</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-0.0062</v>
+        <v>0.39</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6853700</v>
+        <v>8446900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="H22" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
+        <v>70.36</v>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.772</v>
+        <v>0.361</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.716</v>
+        <v>0.243</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1492,19 +1492,19 @@
       <c r="D23" s="2" t="n">
         <v>0.82</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6691300</v>
+        <v>8108800</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="H23" t="n">
         <v>58.27</v>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1526,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>-0.0159</v>
+        <v>0.375</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6556000</v>
+        <v>8061800</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.35</v>
+        <v>1.07</v>
       </c>
       <c r="H24" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
+        <v>65.33</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.306</v>
+        <v>0.347</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.296</v>
+        <v>0.326</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,39 +1571,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.013</v>
+        <v>1.35</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.094</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6504700</v>
+        <v>8039000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.44</v>
+        <v>4.56</v>
       </c>
       <c r="H25" t="n">
-        <v>53.34</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.64</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.775</v>
+        <v>1.493</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.775</v>
+        <v>1.612</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0323</v>
+        <v>0.395</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6429900</v>
+        <v>7817000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.89</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
-        <v>80.19</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.46</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.37</v>
+        <v>0.402</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.352</v>
+        <v>0.409</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,28 +1661,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>-0.0738</v>
+        <v>0.505</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.07339999999999999</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6330700</v>
+        <v>7757300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>3.59</v>
+        <v>1.39</v>
       </c>
       <c r="H27" t="n">
-        <v>26.89</v>
+        <v>25.92</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.496</v>
+        <v>0.584</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.613</v>
+        <v>0.638</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,36 +1706,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.78</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.013</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5440900</v>
+        <v>7534700</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="H28" t="n">
-        <v>41.68</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
+        <v>53.34</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.775</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
     </row>
@@ -1747,39 +1751,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5215000</v>
+        <v>7435100</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2.63</v>
+        <v>0.35</v>
       </c>
       <c r="H29" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.61</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.154</v>
+        <v>0.225</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.152</v>
+        <v>0.241</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1792,39 +1796,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>LUSTER</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E30" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5188100</v>
+        <v>6935400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.6</v>
+        <v>1.28</v>
       </c>
       <c r="H30" t="n">
-        <v>57.36</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.7</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.28</v>
+        <v>0.026</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.303</v>
+        <v>0.028</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1837,39 +1841,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>6786100</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H31" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>0.37</v>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>5076600</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H31" t="n">
-        <v>63.83</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0.347</v>
-      </c>
       <c r="K31" s="2" t="n">
-        <v>0.326</v>
+        <v>0.352</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1882,39 +1886,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>-0.2</v>
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5022000</v>
+        <v>6208700</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H32" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.024</v>
+        <v>4.932</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.024</v>
+        <v>4.669</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1927,39 +1931,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4976300</v>
+        <v>6194300</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H33" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.92</v>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.225</v>
+        <v>0.868</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.241</v>
+        <v>0.869</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1972,39 +1976,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>-0.026</v>
+        <v>0.515</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.0463</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4976300</v>
+        <v>5658000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H34" t="n">
-        <v>63.01</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.356</v>
+        <v>0.521</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.323</v>
+        <v>0.53</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2028,19 +2032,19 @@
       <c r="D35" s="2" t="n">
         <v>0.62</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>-0.0159</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4681300</v>
+        <v>5646100</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H35" t="n">
         <v>54.39</v>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2062,40 +2066,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.0294</v>
+        <v>0.465</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4522100</v>
+        <v>5451600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H36" t="n">
-        <v>40.44</v>
+        <v>41.68</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>0.197</v>
-      </c>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
     </row>
@@ -2107,28 +2107,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.0197</v>
+        <v>0.485</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4503800</v>
+        <v>5391100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="H37" t="n">
-        <v>41.05</v>
+        <v>30.52</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4.716</v>
+        <v>0.521</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4.884</v>
+        <v>0.569</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2152,39 +2152,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.0185</v>
+        <v>2.14</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4375400</v>
+        <v>5385300</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H38" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.18</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.216</v>
+        <v>2.105</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.217</v>
+        <v>2.085</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2197,39 +2197,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.155</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4363200</v>
+        <v>5215000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.23</v>
+        <v>2.63</v>
       </c>
       <c r="H39" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
+        <v>52.49</v>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.868</v>
+        <v>0.154</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.869</v>
+        <v>0.152</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2242,39 +2242,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>-0.0203</v>
+        <v>0.295</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4057600</v>
+        <v>5190900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="H40" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
+        <v>57.36</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.696</v>
+        <v>0.28</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.681</v>
+        <v>0.303</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2287,39 +2287,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0038</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>ARTRONIQ</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2.15</v>
+        <v>0.145</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0357</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4027000</v>
+        <v>5146700</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.21</v>
+        <v>15.81</v>
       </c>
       <c r="H41" t="n">
-        <v>57.43</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
+        <v>79.14</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.106</v>
+        <v>0.134</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.086</v>
+        <v>0.132</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2332,39 +2332,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>-0.0208</v>
+        <v>4.68</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3861900</v>
+        <v>5110600</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="H42" t="n">
-        <v>59.69</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
+        <v>43.18</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.675</v>
+        <v>4.718</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.611</v>
+        <v>4.884</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2377,28 +2377,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3837800</v>
+        <v>5022000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.52</v>
+        <v>0.27</v>
       </c>
       <c r="H43" t="n">
-        <v>31.76</v>
+        <v>28.3</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.521</v>
+        <v>0.024</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.569</v>
+        <v>0.024</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2422,28 +2422,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.225</v>
+        <v>0.37</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3712400</v>
+        <v>5003000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
       <c r="H44" t="n">
-        <v>33.08</v>
+        <v>60.27</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.247</v>
+        <v>0.356</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.301</v>
+        <v>0.323</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2467,39 +2467,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0.0233</v>
+        <v>2.12</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3623700</v>
+        <v>4742100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>3.97</v>
+        <v>0.32</v>
       </c>
       <c r="H45" t="n">
-        <v>75.02</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.24</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.208</v>
+        <v>2.216</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.205</v>
+        <v>2.217</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2512,39 +2512,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3517600</v>
+        <v>4557700</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H46" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.44</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.122</v>
+        <v>0.184</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.125</v>
+        <v>0.197</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2557,39 +2557,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0038</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARTRONIQ</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.7</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3479600</v>
+        <v>4357600</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>10.69</v>
+        <v>0.48</v>
       </c>
       <c r="H47" t="n">
-        <v>79.14</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+        <v>58.5</v>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.134</v>
+        <v>0.675</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.132</v>
+        <v>0.611</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2602,39 +2602,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.725</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0203</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3449500</v>
+        <v>4269400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="H48" t="n">
-        <v>34.47</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.3</v>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.609</v>
+        <v>0.696</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>7.723</v>
+        <v>0.681</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2647,39 +2647,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.0159</v>
+        <v>0.215</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3291000</v>
+        <v>4188200</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>12.01</v>
+        <v>4.59</v>
       </c>
       <c r="H49" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
+        <v>69.34</v>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.294</v>
+        <v>0.208</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.297</v>
+        <v>0.205</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2692,39 +2692,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.185</v>
+        <v>7.31</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.0571</v>
+        <v>0.0069</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3264400</v>
+        <v>4150300</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H50" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.47</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.165</v>
+        <v>7.609</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.166</v>
+        <v>7.723</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2737,39 +2737,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.0125</v>
+        <v>0.22</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3257100</v>
+        <v>4040800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="H51" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.58</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.781</v>
+        <v>0.246</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.773</v>
+        <v>0.301</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2793,14 +2793,14 @@
       <c r="D52" s="2" t="n">
         <v>0.32</v>
       </c>
-      <c r="E52" s="8" t="n">
+      <c r="E52" s="3" t="n">
         <v>-0.04480000000000001</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3230100</v>
+        <v>3779500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="H52" t="n">
         <v>46.76</v>
@@ -2827,28 +2827,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.014</v>
+        <v>0.93</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0363</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3189900</v>
+        <v>3749000</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1.7</v>
+        <v>0.47</v>
       </c>
       <c r="H53" t="n">
-        <v>46.48</v>
+        <v>49.74</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.733</v>
+        <v>0.958</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.748</v>
+        <v>0.826</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2872,39 +2872,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UOADEV</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0067</v>
+        <v>1.18</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.0484</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3078000</v>
+        <v>3626100</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>14.54</v>
+        <v>0.62</v>
       </c>
       <c r="H54" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.57</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.558</v>
+        <v>1.161</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.614</v>
+        <v>1.169</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2917,39 +2917,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>-0.0364</v>
+        <v>0.79</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2981300</v>
+        <v>3552600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.34</v>
+        <v>0.43</v>
       </c>
       <c r="H55" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
+        <v>53.58</v>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.252</v>
+        <v>0.781</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.254</v>
+        <v>0.773</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2962,39 +2962,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>-0.032</v>
+        <v>0.125</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2933800</v>
+        <v>3517600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="H56" t="n">
-        <v>30.96</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.22</v>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.278</v>
+        <v>0.122</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.379</v>
+        <v>0.125</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3007,39 +3007,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.2</v>
+        <v>0.305</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>-0.0317</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2871100</v>
+        <v>3321000</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>12.12</v>
       </c>
       <c r="H57" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.58</v>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.206</v>
+        <v>0.294</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.208</v>
+        <v>0.297</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3052,28 +3052,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>-0.0311</v>
+        <v>1.22</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2807800</v>
+        <v>3309500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="H58" t="n">
-        <v>50.47</v>
+        <v>32.24</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.959</v>
+        <v>1.279</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.826</v>
+        <v>1.379</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3097,39 +3097,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>-0.028</v>
+        <v>0.19</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2743500</v>
+        <v>3264900</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="H59" t="n">
-        <v>45.74</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
+        <v>67.38</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.069</v>
+        <v>0.165</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.038</v>
+        <v>0.166</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3142,39 +3142,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>-0.0177</v>
+        <v>0.73</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.021</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2718400</v>
+        <v>3204500</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.11</v>
+        <v>1.71</v>
       </c>
       <c r="H60" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.17</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4.932</v>
+        <v>0.733</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4.669</v>
+        <v>0.748</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3187,39 +3187,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>-0.0323</v>
+        <v>0.7</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.0411</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2711000</v>
+        <v>3091600</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H61" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.163</v>
+        <v>0.538</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.17</v>
+        <v>0.45</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3232,39 +3232,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>UOADEV</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0</v>
+        <v>1.51</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2679500</v>
+        <v>3078300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1.29</v>
+        <v>14.54</v>
       </c>
       <c r="H62" t="n">
-        <v>80.15000000000001</v>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.9</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.211</v>
+        <v>1.558</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.174</v>
+        <v>1.614</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3277,39 +3277,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>-0.0342</v>
+        <v>0.375</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2658900</v>
+        <v>3067900</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.52</v>
+        <v>2.5</v>
       </c>
       <c r="H63" t="n">
-        <v>80.78</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.07</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.539</v>
+        <v>0.384</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.45</v>
+        <v>0.395</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3322,39 +3322,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0186</v>
+        <v>0.265</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2566900</v>
+        <v>2995800</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="H64" t="n">
-        <v>62.72</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
+        <v>55.66</v>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.775</v>
+        <v>0.252</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.763</v>
+        <v>0.254</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3367,39 +3367,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>-0.0102</v>
+        <v>0.245</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2527300</v>
+        <v>2965300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.78</v>
+        <v>1.43</v>
       </c>
       <c r="H65" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.673</v>
+        <v>0.21</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.309</v>
+        <v>0.174</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3412,28 +3412,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>-0.0042</v>
+        <v>0.215</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2507000</v>
+        <v>2921700</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.25</v>
+        <v>3.76</v>
       </c>
       <c r="H66" t="n">
-        <v>24.08</v>
+        <v>37.92</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7.566</v>
+        <v>0.23</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>8.069000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3457,28 +3457,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>-0.0185</v>
+        <v>0.2</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2378400</v>
+        <v>2921100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.31</v>
+        <v>0.71</v>
       </c>
       <c r="H67" t="n">
-        <v>52.71</v>
+        <v>42.8</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.523</v>
+        <v>0.206</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.531</v>
+        <v>0.208</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3502,28 +3502,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>-0.0133</v>
+        <v>7.2</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2319800</v>
+        <v>2907200</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="H68" t="n">
-        <v>52.46</v>
+        <v>24.32</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.368</v>
+        <v>7.567</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.368</v>
+        <v>8.069000000000001</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3547,39 +3547,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>-0.0331</v>
+        <v>1.04</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2317100</v>
+        <v>2871400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.67</v>
+        <v>0.23</v>
       </c>
       <c r="H69" t="n">
-        <v>61.96</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
+        <v>45.74</v>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.831</v>
+        <v>1.069</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.763</v>
+        <v>1.038</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3592,39 +3592,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2235400</v>
+        <v>2826900</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H70" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
+        <v>72.19</v>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.077</v>
+        <v>0.788</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.926</v>
+        <v>0.766</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3637,39 +3637,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.37</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2208700</v>
+        <v>2756800</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="H71" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.46</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>13.022</v>
+        <v>0.368</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>13.544</v>
+        <v>0.368</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3682,39 +3682,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>6.87</v>
+        <v>0.82</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.0133</v>
+        <v>0.0186</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2120700</v>
+        <v>2746800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.43</v>
+        <v>1.35</v>
       </c>
       <c r="H72" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
+        <v>62.72</v>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5.937</v>
+        <v>0.775</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>5.809</v>
+        <v>0.763</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3727,39 +3727,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>-0.0189</v>
+        <v>6.89</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0162</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2094100</v>
+        <v>2649000</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1.06</v>
+        <v>0.54</v>
       </c>
       <c r="H73" t="n">
-        <v>62.06</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.494</v>
+        <v>5.939</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.481</v>
+        <v>5.809</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3772,39 +3772,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>-0.0174</v>
+        <v>2.93</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2081200</v>
+        <v>2542300</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.21</v>
+        <v>0.78</v>
       </c>
       <c r="H74" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.3</v>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.16</v>
+        <v>2.674</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.121</v>
+        <v>2.309</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3817,39 +3817,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.0133</v>
+        <v>0.87</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.0387</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2056300</v>
+        <v>2541700</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.16</v>
+        <v>0.74</v>
       </c>
       <c r="H75" t="n">
-        <v>42.19</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.83</v>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>10.014</v>
+        <v>0.83</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>10.201</v>
+        <v>0.762</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3862,39 +3862,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0</v>
+        <v>6.17</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1950600</v>
+        <v>2489000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="H76" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.18</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.718</v>
+        <v>6.445</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.695</v>
+        <v>6.818</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.65</v>
+        <v>12.94</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>0.0185</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1933600</v>
+        <v>2483600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H77" t="n">
-        <v>43.76</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
+        <v>41.86</v>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.668</v>
+        <v>13.02</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.78</v>
+        <v>13.543</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3952,28 +3952,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.0123</v>
+        <v>5.65</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1898600</v>
+        <v>2401000</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.24</v>
+        <v>0.18</v>
       </c>
       <c r="H78" t="n">
-        <v>39.23</v>
+        <v>52.5</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.421</v>
+        <v>5.646</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.44</v>
+        <v>5.338</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3997,28 +3997,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1895000</v>
+        <v>2284000</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.14</v>
+        <v>0.71</v>
       </c>
       <c r="H79" t="n">
-        <v>52.5</v>
+        <v>51.91</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>5.646</v>
+        <v>0.865</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>5.338</v>
+        <v>0.859</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4042,39 +4042,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>-0.0083</v>
+        <v>1.12</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1841100</v>
+        <v>2249500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
       <c r="H80" t="n">
-        <v>68.39</v>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
+        <v>62.8</v>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.554</v>
+        <v>1.076</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.498</v>
+        <v>0.926</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4087,28 +4087,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>-0.0364</v>
+        <v>9.94</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1825500</v>
+        <v>2230700</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>3.71</v>
+        <v>0.17</v>
       </c>
       <c r="H81" t="n">
-        <v>36.94</v>
+        <v>42.19</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.266</v>
+        <v>10.014</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.221</v>
+        <v>10.201</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4132,39 +4132,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0</v>
+        <v>-0.0174</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1815800</v>
+        <v>2227600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="H82" t="n">
-        <v>72.19</v>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.97</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.788</v>
+        <v>1.16</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.766</v>
+        <v>1.121</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4177,39 +4177,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>-0.0164</v>
+        <v>0.52</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1805200</v>
+        <v>2206600</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.49</v>
+        <v>1.12</v>
       </c>
       <c r="H83" t="n">
-        <v>72.08</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
+        <v>62.06</v>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.039</v>
+        <v>0.494</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.871</v>
+        <v>0.481</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4222,39 +4222,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0</v>
+        <v>1.64</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1732100</v>
+        <v>2187900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1.03</v>
+        <v>0.33</v>
       </c>
       <c r="H84" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
+        <v>42.16</v>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.212</v>
+        <v>1.667</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.19</v>
+        <v>1.779</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4267,39 +4267,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0</v>
+        <v>4.49</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0205</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1700200</v>
+        <v>2078200</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H85" t="n">
-        <v>86.70999999999999</v>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
+        <v>45.76</v>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>4.486</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.494</v>
+        <v>4.805</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4312,39 +4312,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>-0.0083</v>
+        <v>0.775</v>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1695900</v>
+        <v>2068800</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.76</v>
+        <v>1.07</v>
       </c>
       <c r="H86" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.64</v>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.281</v>
+        <v>0.718</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.31</v>
+        <v>0.695</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4357,39 +4357,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.0488</v>
+        <v>2.1</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1654900</v>
+        <v>2019700</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1.61</v>
+        <v>4.1</v>
       </c>
       <c r="H87" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.68</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.204</v>
+        <v>2.264</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.211</v>
+        <v>2.221</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4402,39 +4402,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>-0.0189</v>
+        <v>1.19</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>-0.0246</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1613900</v>
+        <v>2005200</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="H88" t="n">
-        <v>46.17</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.64</v>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.791</v>
+        <v>1.038</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.806</v>
+        <v>0.871</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4447,39 +4447,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>-0.0435</v>
+        <v>0.6</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1613200</v>
+        <v>1987700</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>2.07</v>
+        <v>0.36</v>
       </c>
       <c r="H89" t="n">
-        <v>40.88</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.39</v>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.231</v>
+        <v>0.554</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.234</v>
+        <v>0.498</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4492,39 +4492,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>-0.0167</v>
+        <v>0.705</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1607200</v>
+        <v>1955800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H90" t="n">
-        <v>52.19</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.64</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.292</v>
+        <v>0.751</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.281</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4537,39 +4537,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.96</v>
+        <v>0.41</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0123</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1603900</v>
+        <v>1906900</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.42</v>
+        <v>1.24</v>
       </c>
       <c r="H91" t="n">
-        <v>34.31</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.993</v>
+        <v>0.421</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.065</v>
+        <v>0.44</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4582,28 +4582,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.38</v>
+        <v>2.83</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1590500</v>
+        <v>1891400</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1.3</v>
+        <v>0.13</v>
       </c>
       <c r="H92" t="n">
-        <v>38.45</v>
+        <v>54.66</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.385</v>
+        <v>2.799</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.395</v>
+        <v>2.703</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4627,39 +4627,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.9</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1585300</v>
+        <v>1874300</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="H93" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.71</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.601</v>
+        <v>1.926</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.583</v>
+        <v>1.956</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4683,19 +4683,19 @@
       <c r="D94" s="2" t="n">
         <v>0.405</v>
       </c>
-      <c r="E94" s="8" t="n">
+      <c r="E94" s="3" t="n">
         <v>-0.0241</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1570200</v>
+        <v>1871300</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H94" t="n">
         <v>56.87</v>
       </c>
-      <c r="I94" s="9" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4717,39 +4717,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>-0.0145</v>
+        <v>0.45</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1551600</v>
+        <v>1854000</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
       <c r="H95" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.84</v>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.348</v>
+        <v>0.451</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.381</v>
+        <v>0.428</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4762,36 +4762,40 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>-0.0286</v>
+        <v>0.785</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1495300</v>
+        <v>1774500</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="H96" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="n"/>
-      <c r="K96" s="2" t="n"/>
+        <v>47.41</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.806</v>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
     </row>
@@ -4803,28 +4807,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>-0.0208</v>
+        <v>1.19</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1491900</v>
+        <v>1761800</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.48</v>
+        <v>0.79</v>
       </c>
       <c r="H97" t="n">
-        <v>46.24</v>
+        <v>31.53</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4832,10 +4836,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.241</v>
+        <v>1.28</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.249</v>
+        <v>1.309</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4848,39 +4852,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>-0.0217</v>
+        <v>0.225</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1479300</v>
+        <v>1740200</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.14</v>
+        <v>1.04</v>
       </c>
       <c r="H98" t="n">
-        <v>50.84</v>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
+        <v>60.95</v>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.451</v>
+        <v>0.212</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.428</v>
+        <v>0.19</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4893,39 +4897,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>6.18</v>
+        <v>0.21</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>0.0131</v>
+        <v>0.0244</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1473900</v>
+        <v>1734300</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.3</v>
+        <v>1.69</v>
       </c>
       <c r="H99" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.02</v>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>6.446</v>
+        <v>0.203</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>6.818</v>
+        <v>0.211</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4938,40 +4942,36 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>-0.018</v>
+        <v>0.345</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1442900</v>
+        <v>1733000</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="H100" t="n">
-        <v>30.92</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0.582</v>
-      </c>
+        <v>69.31</v>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="n"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
     </row>
@@ -4983,39 +4983,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>-0.0163</v>
+        <v>0.96</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1417600</v>
+        <v>1727200</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.27</v>
+        <v>0.46</v>
       </c>
       <c r="H101" t="n">
-        <v>52.28</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.31</v>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.907</v>
+        <v>0.993</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.864</v>
+        <v>1.065</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5028,39 +5028,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>-0.0246</v>
+        <v>0.64</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1382400</v>
+        <v>1720000</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="H102" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.7</v>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>3.594</v>
+        <v>0.601</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.782</v>
+        <v>0.583</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5073,39 +5073,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E103" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1369200</v>
+        <v>1717700</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="H103" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.70999999999999</v>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.338</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.344</v>
+        <v>0.494</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5118,39 +5118,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E104" s="8" t="n">
-        <v>-0.0239</v>
+        <v>0.905</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1330800</v>
+        <v>1713300</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="H104" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.28</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.057</v>
+        <v>0.907</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2.083</v>
+        <v>0.864</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5163,39 +5163,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.62</v>
+        <v>0.335</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1329500</v>
+        <v>1686200</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.45</v>
+        <v>1.28</v>
       </c>
       <c r="H105" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.93</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.613</v>
+        <v>0.348</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.599</v>
+        <v>0.381</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5208,28 +5208,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.445</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.0326</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1291900</v>
+        <v>1679400</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="H106" t="n">
-        <v>58.06</v>
+        <v>47.84</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.252</v>
+        <v>0.457</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.221</v>
+        <v>0.422</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5253,39 +5253,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1289300</v>
+        <v>1607400</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H107" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.19</v>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.756</v>
+        <v>0.292</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.778</v>
+        <v>0.281</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5298,39 +5298,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E108" s="8" t="n">
-        <v>-0.011</v>
+        <v>0.54</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.027</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1288600</v>
+        <v>1592600</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
       <c r="H108" t="n">
-        <v>58.92</v>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.01</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.428</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.414</v>
+        <v>0.582</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5343,39 +5343,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>-0.0229</v>
+        <v>0.235</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1288300</v>
+        <v>1582400</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="H109" t="n">
-        <v>49.77</v>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.275</v>
+        <v>0.241</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.318</v>
+        <v>0.249</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5388,39 +5388,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E110" s="8" t="n">
-        <v>-0.0242</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1286900</v>
+        <v>1564800</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="H110" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.23999999999999</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.614</v>
+        <v>0.756</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.608</v>
+        <v>0.668</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5433,28 +5433,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>-0.0035</v>
+        <v>1.72</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.0282</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1260800</v>
+        <v>1537000</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H111" t="n">
-        <v>55.57</v>
+        <v>35.67</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.8</v>
+        <v>1.814</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2.703</v>
+        <v>1.921</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5478,39 +5478,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E112" s="8" t="n">
-        <v>-0.0328</v>
+        <v>1.26</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>-0.0382</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1203500</v>
+        <v>1497200</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="H112" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
+        <v>47.79</v>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.269</v>
+        <v>1.273</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.266</v>
+        <v>1.317</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5523,39 +5523,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1193400</v>
+        <v>1495600</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>40.08</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.15</v>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.329</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.33</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5568,39 +5568,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E114" s="8" t="n">
-        <v>-0.0248</v>
+        <v>3.56</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1190700</v>
+        <v>1452200</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H114" t="n">
-        <v>43.34</v>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.74</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>3.192</v>
+        <v>3.593</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>3.381</v>
+        <v>2.782</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5613,39 +5613,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E115" s="8" t="n">
-        <v>-0.0179</v>
+        <v>0.455</v>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1158500</v>
+        <v>1438700</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H115" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.72</v>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.288</v>
+        <v>0.429</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.307</v>
+        <v>0.414</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5658,39 +5658,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>4.49</v>
+        <v>7.95</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>0.0205</v>
+        <v>0.0474</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1157900</v>
+        <v>1425000</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.22</v>
+        <v>0.89</v>
       </c>
       <c r="H116" t="n">
-        <v>45.76</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.98</v>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>4.486</v>
+        <v>7.753</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>4.805</v>
+        <v>7.899</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5712,21 +5712,21 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E117" s="8" t="n">
-        <v>-0.0126</v>
+        <v>0.79</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1151000</v>
+        <v>1412300</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H117" t="n">
-        <v>62.14</v>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
+        <v>63.24</v>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5748,39 +5748,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>-0.0105</v>
+        <v>0.33</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1148800</v>
+        <v>1399900</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="H118" t="n">
-        <v>54.34</v>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.04</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.462</v>
+        <v>0.338</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.461</v>
+        <v>0.344</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5793,39 +5793,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>-0.0155</v>
+        <v>2.03</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.0287</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1147700</v>
+        <v>1362800</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="H119" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.47</v>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.318</v>
+        <v>2.056</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.307</v>
+        <v>2.083</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5838,39 +5838,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>-0.0163</v>
+        <v>3.12</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.0341</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1137300</v>
+        <v>1361200</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H120" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.37</v>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.911</v>
+        <v>3.189</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.963</v>
+        <v>3.381</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5883,28 +5883,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.26</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1117400</v>
+        <v>1340900</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="H121" t="n">
-        <v>47.08</v>
+        <v>58.06</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.928</v>
+        <v>0.252</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1.956</v>
+        <v>0.221</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5928,39 +5928,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E122" s="8" t="n">
-        <v>-0.018</v>
+        <v>0.62</v>
+      </c>
+      <c r="E122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1074200</v>
+        <v>1329500</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="H122" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="I122" s="9" t="inlineStr">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.06</v>
+        <v>0.613</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.902</v>
+        <v>0.599</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5973,28 +5973,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.31</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1047800</v>
+        <v>1322700</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H123" t="n">
-        <v>37.75</v>
+        <v>37.81</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.581</v>
+        <v>0.329</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.621</v>
+        <v>0.33</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6018,28 +6018,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.77</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1040000</v>
+        <v>1308100</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="H124" t="n">
-        <v>51.91</v>
+        <v>51.65</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.865</v>
+        <v>1.756</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.859</v>
+        <v>1.778</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6063,39 +6063,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>-0.0319</v>
+        <v>2.43</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1028600</v>
+        <v>1291100</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H125" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.04</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.447</v>
+        <v>2.595</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.451</v>
+        <v>2.776</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6108,39 +6108,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E126" s="8" t="n">
-        <v>-0.024</v>
+        <v>0.61</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1009800</v>
+        <v>1287400</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="H126" t="n">
-        <v>30.61</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.13</v>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>2.596</v>
+        <v>0.615</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2.776</v>
+        <v>0.608</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6153,28 +6153,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E127" s="8" t="n">
-        <v>-0.0282</v>
+        <v>1.28</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>959100</v>
+        <v>1285400</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H127" t="n">
-        <v>35.67</v>
+        <v>43.38</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.814</v>
+        <v>1.319</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1.921</v>
+        <v>1.308</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6198,39 +6198,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E128" s="8" t="n">
-        <v>-0.0062</v>
+        <v>1.1</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>959000</v>
+        <v>1269600</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="H128" t="n">
-        <v>79.31999999999999</v>
-      </c>
-      <c r="I128" s="9" t="inlineStr">
+        <v>62.63</v>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.061</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.627</v>
+        <v>0.902</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6243,39 +6243,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E129" s="8" t="n">
-        <v>-0.018</v>
+        <v>0.275</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>950300</v>
+        <v>1219400</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H129" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.85</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.757</v>
+        <v>0.288</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.668</v>
+        <v>0.307</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6288,39 +6288,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>0</v>
+        <v>8.01</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>904000</v>
+        <v>1215300</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H130" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="I130" s="9" t="inlineStr">
+        <v>73.19</v>
+      </c>
+      <c r="I130" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.641</v>
+        <v>7.317</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.604</v>
+        <v>6.791</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6333,39 +6333,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>897900</v>
+        <v>1203500</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.1</v>
+        <v>1.25</v>
       </c>
       <c r="H131" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
+        <v>72.34999999999999</v>
+      </c>
+      <c r="I131" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>3.993</v>
+        <v>0.269</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>3.468</v>
+        <v>0.266</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6378,39 +6378,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>4.27</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0071</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>875600</v>
+        <v>1199900</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.41</v>
+        <v>0.14</v>
       </c>
       <c r="H132" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="I132" s="9" t="inlineStr">
+        <v>65.27</v>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>3.994</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>3.468</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6423,39 +6423,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E133" s="8" t="n">
-        <v>-0.0146</v>
+        <v>0.33</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>870100</v>
+        <v>1196100</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.25</v>
+        <v>2.54</v>
       </c>
       <c r="H133" t="n">
-        <v>57.04</v>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.301</v>
+        <v>0.313</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>1.202</v>
+        <v>0.316</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6468,39 +6468,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E134" s="8" t="n">
-        <v>-0.0182</v>
+        <v>5.95</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>869400</v>
+        <v>1158800</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="H134" t="n">
-        <v>68.15000000000001</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
+        <v>64.09</v>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.483</v>
+        <v>5.523</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.454</v>
+        <v>5.375</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6513,39 +6513,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0.0038</v>
+        <v>0.905</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>859200</v>
+        <v>1155100</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="H135" t="n">
-        <v>72.91</v>
-      </c>
-      <c r="I135" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.8</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>7.315</v>
+        <v>0.911</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>6.791</v>
+        <v>0.963</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6558,39 +6558,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.47</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>836300</v>
+        <v>1149300</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.14</v>
+        <v>0.61</v>
       </c>
       <c r="H136" t="n">
-        <v>58.03</v>
-      </c>
-      <c r="I136" s="9" t="inlineStr">
+        <v>54.34</v>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2.636</v>
+        <v>0.462</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.588</v>
+        <v>0.461</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6603,39 +6603,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="E137" s="8" t="n">
-        <v>-0.0017</v>
+        <v>0.255</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>804600</v>
+        <v>1142500</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.23</v>
+        <v>0.64</v>
       </c>
       <c r="H137" t="n">
-        <v>62.76</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.4</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>5.517</v>
+        <v>0.235</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>5.374</v>
+        <v>0.209</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6648,39 +6648,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E138" s="8" t="n">
-        <v>-0.0157</v>
+        <v>2.73</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>801600</v>
+        <v>1094600</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="H138" t="n">
-        <v>46</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.38</v>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.637</v>
+        <v>2.638</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.612</v>
+        <v>2.588</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6693,39 +6693,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.455</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>768300</v>
+        <v>1048100</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.08</v>
+        <v>0.44</v>
       </c>
       <c r="H139" t="n">
-        <v>58.15</v>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
+        <v>53.37</v>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>2.787</v>
+        <v>0.447</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>2.612</v>
+        <v>0.451</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6738,39 +6738,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>RCECAP</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1.01</v>
+        <v>0.555</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>0.0254</v>
+        <v>0.0183</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>737900</v>
+        <v>1047800</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="I140" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.75</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.983</v>
+        <v>0.581</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1.014</v>
+        <v>0.621</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6783,39 +6783,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>1.22</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>719000</v>
+        <v>1010800</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
       <c r="H141" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
+        <v>64.17</v>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.094</v>
+        <v>1.098</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.041</v>
+        <v>0.841</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6828,39 +6828,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E142" s="8" t="n">
-        <v>-0.0315</v>
+        <v>0.675</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>715000</v>
+        <v>1009400</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H142" t="n">
-        <v>65.12</v>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
+        <v>65.2</v>
+      </c>
+      <c r="I142" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.099</v>
+        <v>0.641</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0.842</v>
+        <v>0.604</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6873,39 +6873,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E143" s="8" t="n">
-        <v>-0.0167</v>
+        <v>0.54</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>707800</v>
+        <v>976800</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="H143" t="n">
-        <v>37.34</v>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.15000000000001</v>
+      </c>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.614</v>
+        <v>0.483</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.634</v>
+        <v>0.454</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6918,39 +6918,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>0</v>
+        <v>-0.0062</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>705100</v>
+        <v>972800</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="H144" t="n">
-        <v>25.54</v>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.31999999999999</v>
+      </c>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.952</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.99</v>
+        <v>0.627</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6963,39 +6963,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0.0077</v>
+        <v>1.35</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>661900</v>
+        <v>942100</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H145" t="n">
-        <v>61.06</v>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.04</v>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.625</v>
+        <v>1.301</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.533</v>
+        <v>1.202</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -7008,28 +7008,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>0</v>
+        <v>3.36</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0.003</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>657800</v>
+        <v>905400</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H146" t="n">
-        <v>33.64</v>
+        <v>37.46</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.753</v>
+        <v>3.458</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>3.646</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7053,39 +7053,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.26</v>
+        <v>7.86</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>0</v>
+        <v>-0.0025</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>641100</v>
+        <v>884100</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H147" t="n">
-        <v>50.56</v>
-      </c>
-      <c r="I147" s="9" t="inlineStr">
+        <v>48.93</v>
+      </c>
+      <c r="I147" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.25</v>
+        <v>7.888</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1.284</v>
+        <v>7.855</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7098,39 +7098,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>0</v>
+        <v>2.13</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>628500</v>
+        <v>852000</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="H148" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.69</v>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1.876</v>
+        <v>2.093</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>2.01</v>
+        <v>2.041</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7143,28 +7143,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E149" s="8" t="n">
-        <v>-0.0145</v>
+        <v>1.81</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>626600</v>
+        <v>841700</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="H149" t="n">
-        <v>34.87</v>
+        <v>35.35</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>2.197</v>
+        <v>1.875</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>2.31</v>
+        <v>2.009</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7188,39 +7188,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E150" s="8" t="n">
-        <v>-0.0102</v>
+        <v>2.88</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>617900</v>
+        <v>840500</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H150" t="n">
-        <v>44.35</v>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.66</v>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>2.971</v>
+        <v>2.788</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>3.033</v>
+        <v>2.612</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7242,19 +7242,19 @@
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.74</v>
+      </c>
+      <c r="E151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>605900</v>
+        <v>831100</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H151" t="n">
-        <v>47.17</v>
+        <v>46.05</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7278,39 +7278,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E152" s="8" t="n">
-        <v>-0.0033</v>
+        <v>2.92</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>586600</v>
+        <v>821800</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H152" t="n">
-        <v>68.89</v>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.35</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2.726</v>
+        <v>2.971</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.073</v>
+        <v>3.033</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7323,28 +7323,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E153" s="8" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.625</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>548500</v>
+        <v>816500</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="H153" t="n">
-        <v>18.68</v>
+        <v>46</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.021</v>
+        <v>0.637</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.113</v>
+        <v>0.612</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7368,28 +7368,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>529200</v>
+        <v>774200</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="H154" t="n">
-        <v>72.15000000000001</v>
+        <v>61.87</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1.249</v>
+        <v>0.625</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>1.019</v>
+        <v>0.533</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7413,39 +7413,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E155" s="8" t="n">
-        <v>-0.0296</v>
+        <v>0.9</v>
+      </c>
+      <c r="E155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>526400</v>
+        <v>756900</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1.02</v>
+        <v>0.31</v>
       </c>
       <c r="H155" t="n">
-        <v>48.27</v>
-      </c>
-      <c r="I155" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.54</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.824</v>
+        <v>0.952</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.838</v>
+        <v>0.99</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7458,39 +7458,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>RCECAP</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>7.84</v>
+        <v>1</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>0.0329</v>
+        <v>0.0152</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>526200</v>
+        <v>746100</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.33</v>
+        <v>1.32</v>
       </c>
       <c r="H156" t="n">
-        <v>52.58</v>
-      </c>
-      <c r="I156" s="9" t="inlineStr">
+        <v>55.68</v>
+      </c>
+      <c r="I156" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>7.742</v>
+        <v>0.982</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>7.897</v>
+        <v>1.014</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7503,39 +7503,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E157" s="8" t="n">
-        <v>-0.0347</v>
+        <v>1.26</v>
+      </c>
+      <c r="E157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>518000</v>
+        <v>726100</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H157" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="I157" s="9" t="inlineStr">
+        <v>50.56</v>
+      </c>
+      <c r="I157" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>1.664</v>
+        <v>1.25</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1.677</v>
+        <v>1.284</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7548,28 +7548,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E158" s="8" t="n">
-        <v>-0.0309</v>
+        <v>0.595</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>513100</v>
+        <v>712800</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="H158" t="n">
-        <v>33.04</v>
+        <v>38.97</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.679</v>
+        <v>0.615</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1.81</v>
+        <v>0.634</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7593,45 +7593,900 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>502100</v>
+        <v>700900</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H159" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I159" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>3.02</v>
+        <v>2.957</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>2.817</v>
+        <v>2.835</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>643100</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H160" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>639600</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H161" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>1.811</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>629600</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H162" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>-0.0242</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>604100</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H163" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="I163" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>602700</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H164" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="I164" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>602300</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H165" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="I165" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>2.726</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>602300</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H166" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="I166" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>1.616</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="E167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>590100</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H167" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>5.691</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>5.859</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5142</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>WASCO</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-0.0327</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>586100</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H168" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="I168" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>582000</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H169" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>-0.0108</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>577300</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H170" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>575700</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H171" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I171" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>TEOSENG</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>-0.0237</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>571400</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>50.41</v>
+      </c>
+      <c r="I172" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>567400</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H173" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>548200</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H174" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>7.389</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>540500</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H175" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>535000</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>527800</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H177" t="n">
+        <v>62.23</v>
+      </c>
+      <c r="I177" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>2.817</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>524800</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H178" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="I178" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>2.573</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M159"/>
+  <autoFilter ref="A1:M178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
+++ b/docs/downloads/2026-10-12/bursa-report-2026-10-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-12" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-12'!$A$1:$M$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M205"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.0588</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>135601900</v>
+        <v>136428800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H2" t="n">
         <v>23.09</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.058</v>
+        <v>-0.0725</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>110471600</v>
+        <v>112016500</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
-        <v>68.2</v>
+        <v>66.06</v>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.1862</v>
+        <v>-0.1915</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>57666500</v>
+        <v>58332700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>14.9</v>
+        <v>15.07</v>
       </c>
       <c r="H4" t="n">
-        <v>21.97</v>
+        <v>21.66</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.864</v>
+        <v>1.863</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>2.014</v>
@@ -693,7 +693,7 @@
         <v>-0.0278</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>39669600</v>
+        <v>39759600</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0.61</v>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.019</v>
+        <v>0.0237</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>32478600</v>
+        <v>32679700</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1.22</v>
       </c>
       <c r="H6" t="n">
-        <v>76.94</v>
+        <v>77.27</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.852</v>
+        <v>1.853</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.658</v>
+        <v>1.659</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.0414</v>
+        <v>-0.0473</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>30410700</v>
+        <v>30932300</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.42</v>
       </c>
       <c r="H7" t="n">
-        <v>56.71</v>
+        <v>55.85</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0.713</v>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.515</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>18546000</v>
+        <v>19958000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.57</v>
+        <v>0.87</v>
       </c>
       <c r="H8" t="n">
-        <v>60.66</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.99</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.493</v>
+        <v>0.196</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.48</v>
+        <v>0.184</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.19</v>
+        <v>0.515</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17472800</v>
+        <v>18548000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.76</v>
+        <v>0.58</v>
       </c>
       <c r="H9" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.66</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.196</v>
+        <v>0.493</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.184</v>
+        <v>0.48</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -918,10 +918,10 @@
         <v>0.0667</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17133300</v>
+        <v>17562200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="H10" t="n">
         <v>75.65000000000001</v>
@@ -948,33 +948,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>2.85</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.0289</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>16484900</v>
+        <v>16557100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>68.37</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>2.511</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,40 +993,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0.0289</v>
+        <v>0.245</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>16300400</v>
+        <v>16495300</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H12" t="n">
-        <v>68.37</v>
+        <v>0.47</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>2.647</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>2.511</v>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1031,39 +1031,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.1409</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>15658000</v>
+        <v>16174000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.48</v>
+        <v>9.18</v>
       </c>
       <c r="H13" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.62</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.156</v>
+        <v>1.487</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.157</v>
+        <v>1.611</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-0.1342</v>
+        <v>0.155</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>15153900</v>
+        <v>15658000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>8.6</v>
+        <v>0.48</v>
       </c>
       <c r="H14" t="n">
-        <v>21.11</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.1</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.488</v>
+        <v>0.156</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.611</v>
+        <v>0.157</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.016</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>14065800</v>
+        <v>15551400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
-        <v>68.95999999999999</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.586</v>
+        <v>0.585</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0.51</v>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.215</v>
+        <v>0.615</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.0444</v>
+        <v>-0.0238</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>13975900</v>
+        <v>15377700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="H16" t="n">
-        <v>30.21</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.32</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.246</v>
+        <v>0.584</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.301</v>
+        <v>0.523</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.31</v>
+        <v>0.215</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0444</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>13517100</v>
+        <v>14204600</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="H17" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.21</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.306</v>
+        <v>0.246</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.296</v>
+        <v>0.301</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.62</v>
+        <v>0.305</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0317</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>13339200</v>
+        <v>13522500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="H18" t="n">
-        <v>60.44</v>
+        <v>50.85</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.584</v>
+        <v>0.306</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.523</v>
+        <v>0.296</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>0.105</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>12792200</v>
+        <v>12819000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H19" t="n">
-        <v>41.8</v>
+        <v>37.13</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0.122</v>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>12727200</v>
+        <v>12761200</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.8</v>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>12394900</v>
+        <v>12451800</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="H21" t="n">
-        <v>46.92</v>
+        <v>59.12</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.868</v>
+        <v>0.773</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.869</v>
+        <v>0.716</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,28 +1436,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>12361100</v>
+        <v>12448900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="H22" t="n">
-        <v>59.12</v>
+        <v>46.92</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.773</v>
+        <v>0.868</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.716</v>
+        <v>0.869</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1481,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.41</v>
+        <v>0.495</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.0575</v>
+        <v>-0.0917</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>12125000</v>
+        <v>12428000</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.51</v>
+        <v>2.23</v>
       </c>
       <c r="H23" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.71</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.41</v>
+        <v>0.583</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.349</v>
+        <v>0.638</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.495</v>
+        <v>0.41</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.0917</v>
+        <v>-0.0575</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>11851400</v>
+        <v>12181400</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.13</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.19</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.583</v>
+        <v>0.41</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.638</v>
+        <v>0.349</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,39 +1571,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.0526</v>
+        <v>0.39</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10797700</v>
+        <v>11140500</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H25" t="n">
-        <v>24.17</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.36</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.54</v>
+        <v>0.361</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.737</v>
+        <v>0.243</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.455</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.0421</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10719500</v>
+        <v>11022400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="H26" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.62</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.774</v>
+        <v>0.54</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.775</v>
+        <v>0.737</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,39 +1661,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.555</v>
+        <v>0.775</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.0571</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9946400</v>
+        <v>10719500</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="H27" t="n">
-        <v>60.79</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.45</v>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.516</v>
+        <v>0.774</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.441</v>
+        <v>0.775</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,39 +1706,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.0556</v>
+        <v>0.0667</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9911400</v>
+        <v>10000500</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1.32</v>
+        <v>0.62</v>
       </c>
       <c r="H28" t="n">
-        <v>66.70999999999999</v>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.5</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.348</v>
+        <v>0.516</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.326</v>
+        <v>0.441</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1751,39 +1751,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.22</v>
+        <v>0.375</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.0233</v>
+        <v>0.0417</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9566800</v>
+        <v>9982900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.45</v>
+        <v>1.32</v>
       </c>
       <c r="H29" t="n">
-        <v>43.61</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.33</v>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.225</v>
+        <v>0.347</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.241</v>
+        <v>0.326</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,28 +1796,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-0.0519</v>
+        <v>0.22</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9423300</v>
+        <v>9637000</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1.11</v>
+        <v>0.45</v>
       </c>
       <c r="H30" t="n">
-        <v>57.75</v>
+        <v>43.61</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.355</v>
+        <v>0.225</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.323</v>
+        <v>0.241</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1841,28 +1841,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.11</v>
+        <v>0.365</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.0231</v>
+        <v>-0.0519</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9351800</v>
+        <v>9517800</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.64</v>
+        <v>1.12</v>
       </c>
       <c r="H31" t="n">
-        <v>39.53</v>
+        <v>57.75</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.215</v>
+        <v>0.355</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.217</v>
+        <v>0.323</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1886,39 +1886,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>2.11</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0231</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9140000</v>
+        <v>9467900</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.25</v>
+        <v>0.64</v>
       </c>
       <c r="H32" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.53</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.361</v>
+        <v>2.215</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.243</v>
+        <v>2.217</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1946,10 +1946,10 @@
         <v>-0.0177</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8985600</v>
+        <v>9276100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H33" t="n">
         <v>56.45</v>
@@ -1976,39 +1976,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8471600</v>
+        <v>8569500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.76</v>
+        <v>2.52</v>
       </c>
       <c r="H34" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.2</v>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.402</v>
+        <v>0.369</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.409</v>
+        <v>0.352</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2021,39 +2021,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0.0108</v>
+        <v>0.39</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8466400</v>
+        <v>8543300</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2.49</v>
+        <v>0.77</v>
       </c>
       <c r="H35" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.82</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.369</v>
+        <v>0.401</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.352</v>
+        <v>0.409</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
         <v>-0.0833</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>8234000</v>
+        <v>8234800</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>1.65</v>
@@ -2111,39 +2111,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LUSTER</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>4.67</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6935400</v>
+        <v>7283800</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.28</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.14</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.026</v>
+        <v>4.717</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.028</v>
+        <v>4.884</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2156,39 +2156,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>LUSTER</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0.0263</v>
+        <v>0.025</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6777200</v>
+        <v>6935400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.42</v>
+        <v>1.28</v>
       </c>
       <c r="H38" t="n">
-        <v>44.19</v>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.7</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.719</v>
+        <v>0.026</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4.884</v>
+        <v>0.028</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2201,28 +2201,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.515</v>
+        <v>0.48</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-0.0463</v>
+        <v>-0.04</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6360500</v>
+        <v>6591400</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H39" t="n">
-        <v>47.73</v>
+        <v>29.38</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.521</v>
+        <v>0.52</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.53</v>
+        <v>0.569</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2246,39 +2246,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.52</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6358800</v>
+        <v>6400500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="H40" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.29</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.105</v>
+        <v>0.522</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.085</v>
+        <v>0.53</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2291,28 +2291,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-0.0159</v>
+        <v>2.14</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>6196400</v>
+        <v>6393000</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="H41" t="n">
-        <v>54.39</v>
+        <v>56.18</v>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.613</v>
+        <v>2.105</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.612</v>
+        <v>2.085</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2336,39 +2336,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.62</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5899000</v>
+        <v>6196400</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="H42" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7.608</v>
+        <v>0.613</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>7.723</v>
+        <v>0.612</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2381,28 +2381,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-0.03</v>
+        <v>7.31</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5827200</v>
+        <v>5943800</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.79</v>
+        <v>0.42</v>
       </c>
       <c r="H43" t="n">
-        <v>30.52</v>
+        <v>34.47</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.521</v>
+        <v>7.609</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.569</v>
+        <v>7.723</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         <v>-0.0597</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5714600</v>
+        <v>5746600</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H44" t="n">
         <v>44.58</v>
@@ -2486,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5545100</v>
+        <v>5717600</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H45" t="n">
         <v>57.36</v>
@@ -2557,28 +2557,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0038</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>ARTRONIQ</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>0.15</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5215000</v>
+        <v>5347200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2.63</v>
+        <v>16.43</v>
       </c>
       <c r="H47" t="n">
-        <v>52.49</v>
+        <v>82.88</v>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.154</v>
+        <v>0.134</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.152</v>
+        <v>0.132</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2602,28 +2602,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0038</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ARTRONIQ</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>0.0357</v>
+        <v>0.155</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>5147200</v>
+        <v>5215000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>15.82</v>
+        <v>2.63</v>
       </c>
       <c r="H48" t="n">
-        <v>79.14</v>
+        <v>52.49</v>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.134</v>
+        <v>0.154</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.132</v>
+        <v>0.152</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         <v>-0.027</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4987100</v>
+        <v>5012500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H51" t="n">
         <v>56.16</v>
@@ -2782,39 +2782,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.185</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4777900</v>
+        <v>4950500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>6.14</v>
+        <v>0.92</v>
       </c>
       <c r="H52" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.31999999999999</v>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.23</v>
+        <v>0.165</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.234</v>
+        <v>0.166</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2827,39 +2827,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-0.0278</v>
+        <v>0.175</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4763000</v>
+        <v>4914400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.44</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.675</v>
+        <v>0.184</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.611</v>
+        <v>0.197</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2872,28 +2872,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>0.0857</v>
+        <v>0.7</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4730500</v>
+        <v>4857900</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="H54" t="n">
-        <v>67.38</v>
+        <v>58.5</v>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.165</v>
+        <v>0.675</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.166</v>
+        <v>0.611</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.925</v>
+        <v>0.93</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.0415</v>
+        <v>-0.0363</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4697900</v>
+        <v>4821600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H55" t="n">
-        <v>49.04</v>
+        <v>49.74</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2962,28 +2962,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <v>0.0294</v>
+        <v>0.215</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>4593700</v>
+        <v>4821200</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.65</v>
+        <v>6.2</v>
       </c>
       <c r="H56" t="n">
-        <v>40.44</v>
+        <v>37.92</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.184</v>
+        <v>0.23</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.197</v>
+        <v>0.234</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3007,39 +3007,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>4345900</v>
+        <v>4677200</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>4.76</v>
+        <v>0.57</v>
       </c>
       <c r="H57" t="n">
-        <v>69.34</v>
-      </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.24</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.208</v>
+        <v>1.279</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.205</v>
+        <v>1.379</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3052,39 +3052,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>-0.0374</v>
+        <v>4.49</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0.0205</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>4328000</v>
+        <v>4476700</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="H58" t="n">
-        <v>44.35</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.76</v>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.068</v>
+        <v>4.486</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.038</v>
+        <v>4.805</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3097,39 +3097,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>0.0205</v>
+        <v>1.03</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.0374</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>4169300</v>
+        <v>4439900</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="H59" t="n">
-        <v>45.76</v>
-      </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.35</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4.486</v>
+        <v>1.068</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.805</v>
+        <v>1.038</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3142,39 +3142,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>-0.0357</v>
+        <v>0.215</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>4034600</v>
+        <v>4406400</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.55</v>
+        <v>4.83</v>
       </c>
       <c r="H60" t="n">
-        <v>31.04</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.34</v>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.288</v>
+        <v>0.208</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.306</v>
+        <v>0.205</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3187,28 +3187,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.27</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>4013000</v>
+        <v>4058600</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H61" t="n">
-        <v>27.55</v>
+        <v>31.04</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6.443</v>
+        <v>0.288</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>6.817</v>
+        <v>0.306</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3232,39 +3232,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>-0.0323</v>
+        <v>6.15</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3995500</v>
+        <v>4030700</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="H62" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.55</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.163</v>
+        <v>6.443</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.17</v>
+        <v>6.817</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3277,39 +3277,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E63" s="9" t="n">
-        <v>0.0185</v>
+        <v>0.695</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0347</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3952500</v>
+        <v>4027900</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H63" t="n">
-        <v>43.76</v>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.92</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.668</v>
+        <v>0.75</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1.78</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3322,39 +3322,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.024</v>
+        <v>-0.0323</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3860300</v>
+        <v>3997600</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="H64" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.23</v>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.279</v>
+        <v>1.163</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.379</v>
+        <v>1.17</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3367,39 +3367,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>-0.0347</v>
+        <v>1.66</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3851600</v>
+        <v>3977600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H65" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.28</v>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.75</v>
+        <v>1.669</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3412,28 +3412,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>-0.0616</v>
+        <v>0.2</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>0.08109999999999999</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3837700</v>
+        <v>3873000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.75</v>
+        <v>3.53</v>
       </c>
       <c r="H66" t="n">
-        <v>76.26000000000001</v>
+        <v>63.92</v>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.537</v>
+        <v>0.184</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.449</v>
+        <v>0.183</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3457,28 +3457,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.0548</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3808000</v>
+        <v>3862700</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>3.47</v>
+        <v>0.76</v>
       </c>
       <c r="H67" t="n">
-        <v>63.92</v>
+        <v>77.34</v>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.184</v>
+        <v>0.537</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.183</v>
+        <v>0.449</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3502,39 +3502,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.058</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3798200</v>
+        <v>3843300</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H68" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.93</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.122</v>
+        <v>0.359</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.125</v>
+        <v>0.382</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3547,39 +3547,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.79</v>
+        <v>7.19</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.0125</v>
+        <v>-0.0042</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3756300</v>
+        <v>3825100</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H69" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.08</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.781</v>
+        <v>7.566</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.773</v>
+        <v>8.069000000000001</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3592,39 +3592,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>-0.058</v>
+        <v>0.125</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3739300</v>
+        <v>3801000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H70" t="n">
-        <v>28.93</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.22</v>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.359</v>
+        <v>0.122</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.382</v>
+        <v>0.125</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3637,39 +3637,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>7.2</v>
+        <v>0.79</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.0028</v>
+        <v>-0.0125</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3731600</v>
+        <v>3757300</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="H71" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.58</v>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7.567</v>
+        <v>0.781</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>8.069000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3691,19 +3691,19 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.825</v>
+        <v>0.82</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.0248</v>
+        <v>0.0186</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>3647400</v>
+        <v>3651400</v>
       </c>
       <c r="G72" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="H72" t="n">
-        <v>63.6</v>
+        <v>62.72</v>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0.763</v>
@@ -3736,19 +3736,19 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>-0.0228</v>
+        <v>-0.0246</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>3534500</v>
+        <v>3556900</v>
       </c>
       <c r="G73" s="5" t="n">
         <v>0.26</v>
       </c>
       <c r="H73" t="n">
-        <v>49.26</v>
+        <v>48.88</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3772,28 +3772,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.305</v>
+        <v>0.87</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>-0.0317</v>
+        <v>-0.0387</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>3321000</v>
+        <v>3342400</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>12.12</v>
+        <v>0.97</v>
       </c>
       <c r="H74" t="n">
-        <v>56.58</v>
+        <v>60.83</v>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.294</v>
+        <v>0.83</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.297</v>
+        <v>0.762</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3817,39 +3817,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1.27</v>
+        <v>0.305</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>-0.0155</v>
+        <v>-0.0317</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>3306000</v>
+        <v>3321000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.33</v>
+        <v>12.12</v>
       </c>
       <c r="H75" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.58</v>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.318</v>
+        <v>0.294</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1.307</v>
+        <v>0.297</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3862,28 +3862,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LBS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.375</v>
+        <v>1.28</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.0132</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>3230100</v>
+        <v>3317700</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>2.63</v>
+        <v>0.33</v>
       </c>
       <c r="H76" t="n">
-        <v>33.07</v>
+        <v>43.38</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.384</v>
+        <v>1.319</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.395</v>
+        <v>1.308</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3907,28 +3907,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.245</v>
+        <v>1.11</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.0263</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>3221300</v>
+        <v>3263700</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1.55</v>
+        <v>0.35</v>
       </c>
       <c r="H77" t="n">
-        <v>75.68000000000001</v>
+        <v>60.84</v>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.21</v>
+        <v>1.075</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.174</v>
+        <v>0.926</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3952,39 +3952,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.735</v>
+        <v>6.85</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>0.028</v>
+        <v>0.0103</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>3219200</v>
+        <v>3253500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.72</v>
+        <v>0.66</v>
       </c>
       <c r="H78" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.04000000000001</v>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.734</v>
+        <v>5.935</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.748</v>
+        <v>5.808</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3997,39 +3997,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>0.0103</v>
+        <v>0.375</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>3214000</v>
+        <v>3230600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.65</v>
+        <v>2.63</v>
       </c>
       <c r="H79" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.07</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>5.935</v>
+        <v>0.384</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>5.808</v>
+        <v>0.395</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4042,39 +4042,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.25</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>3197200</v>
+        <v>3230200</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.99</v>
+        <v>1.56</v>
       </c>
       <c r="H80" t="n">
-        <v>51.91</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.15000000000001</v>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.865</v>
+        <v>0.211</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.859</v>
+        <v>0.174</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4087,39 +4087,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0</v>
+        <v>0.735</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0.028</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>3195100</v>
+        <v>3219200</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.53</v>
+        <v>1.72</v>
       </c>
       <c r="H81" t="n">
-        <v>72.19</v>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.75</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.788</v>
+        <v>0.734</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.766</v>
+        <v>0.748</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4132,39 +4132,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.11</v>
+        <v>0.865</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.0263</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>3194200</v>
+        <v>3197200</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.34</v>
+        <v>0.99</v>
       </c>
       <c r="H82" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.91</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.075</v>
+        <v>0.865</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.926</v>
+        <v>0.859</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4177,28 +4177,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>-0.0331</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>3182000</v>
+        <v>3195600</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.93</v>
+        <v>0.53</v>
       </c>
       <c r="H83" t="n">
-        <v>61.96</v>
+        <v>72.19</v>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.831</v>
+        <v>0.788</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4237,7 +4237,7 @@
         <v>-0.014</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3160100</v>
+        <v>3166200</v>
       </c>
       <c r="G84" s="5" t="n">
         <v>0.22</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>3130200</v>
+        <v>3151700</v>
       </c>
       <c r="G85" s="5" t="n">
         <v>0.44</v>
@@ -4312,28 +4312,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UOADEV</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.51</v>
+        <v>0.205</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>0.0067</v>
+        <v>0.025</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>3127100</v>
+        <v>3148200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>14.77</v>
+        <v>0.76</v>
       </c>
       <c r="H86" t="n">
-        <v>27.9</v>
+        <v>48.37</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.558</v>
+        <v>0.207</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.614</v>
+        <v>0.208</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4357,28 +4357,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>UOADEV</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
+        <v>1.51</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>3048200</v>
+        <v>3127100</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.74</v>
+        <v>14.77</v>
       </c>
       <c r="H87" t="n">
-        <v>42.8</v>
+        <v>27.9</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.206</v>
+        <v>1.558</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.208</v>
+        <v>1.614</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4402,39 +4402,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.265</v>
+        <v>1.12</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>-0.0364</v>
+        <v>-0.0261</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>3008200</v>
+        <v>3059600</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1.35</v>
+        <v>0.32</v>
       </c>
       <c r="H88" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.252</v>
+        <v>1.159</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.254</v>
+        <v>1.121</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4447,28 +4447,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2920200</v>
+        <v>3008200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="H89" t="n">
-        <v>64.43000000000001</v>
+        <v>55.66</v>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.613</v>
+        <v>0.252</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.599</v>
+        <v>0.254</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4492,28 +4492,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>-0.0602</v>
+        <v>12.98</v>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2905700</v>
+        <v>2990200</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H90" t="n">
-        <v>51.98</v>
+        <v>43.82</v>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.386</v>
+        <v>13.023</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.375</v>
+        <v>13.544</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4537,28 +4537,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="E91" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.395</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.0482</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2874200</v>
+        <v>2930700</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="H91" t="n">
-        <v>41.86</v>
+        <v>53.51</v>
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>13.02</v>
+        <v>0.387</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>13.543</v>
+        <v>0.376</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4582,39 +4582,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>-0.0348</v>
+        <v>0.62</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2863500</v>
+        <v>2920200</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.158</v>
+        <v>0.613</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.121</v>
+        <v>0.599</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4627,28 +4627,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>-0.028</v>
+        <v>9.93</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2815900</v>
+        <v>2907000</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.53</v>
+        <v>0.22</v>
       </c>
       <c r="H93" t="n">
-        <v>30.04</v>
+        <v>41.48</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.595</v>
+        <v>10.013</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2.776</v>
+        <v>10.201</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4687,10 +4687,10 @@
         <v>-0.0328</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2799000</v>
+        <v>2849100</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H94" t="n">
         <v>69.25</v>
@@ -4717,28 +4717,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="E95" s="9" t="n">
-        <v>0.0122</v>
+        <v>2.42</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.032</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2779900</v>
+        <v>2831700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="H95" t="n">
-        <v>41.48</v>
+        <v>29.5</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>10.013</v>
+        <v>2.594</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>10.201</v>
+        <v>2.776</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2712600</v>
+        <v>2804400</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>5.51</v>
+        <v>5.7</v>
       </c>
       <c r="H96" t="n">
-        <v>39.75</v>
+        <v>42.15</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.27</v>
+        <v>2.273</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2.222</v>
+        <v>2.223</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4807,28 +4807,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>2.91</v>
+        <v>0.295</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>-0.0136</v>
+        <v>-0.0167</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2615700</v>
+        <v>2738200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.8</v>
+        <v>0.22</v>
       </c>
       <c r="H97" t="n">
-        <v>74.13</v>
+        <v>52.19</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.672</v>
+        <v>0.292</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2.309</v>
+        <v>0.281</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4852,39 +4852,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.78</v>
+        <v>0.585</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.0331</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2518500</v>
+        <v>2677200</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="H98" t="n">
-        <v>46.17</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.92</v>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.791</v>
+        <v>0.553</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.806</v>
+        <v>0.498</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4897,39 +4897,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.545</v>
+        <v>2.94</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.018</v>
+        <v>-0.0034</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2435400</v>
+        <v>2667700</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="H99" t="n">
-        <v>30.92</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.43000000000001</v>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.675</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.582</v>
+        <v>2.31</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4942,28 +4942,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1.18</v>
+        <v>0.78</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>-0.0248</v>
+        <v>-0.0189</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2415300</v>
+        <v>2608500</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1.08</v>
+        <v>0.62</v>
       </c>
       <c r="H100" t="n">
-        <v>30.53</v>
+        <v>46.17</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.279</v>
+        <v>0.791</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1.309</v>
+        <v>0.806</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4987,39 +4987,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.44</v>
+        <v>0.545</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.0435</v>
+        <v>-0.018</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2391700</v>
+        <v>2588300</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.23</v>
+        <v>0.63</v>
       </c>
       <c r="H101" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.92</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.45</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.428</v>
+        <v>0.582</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5032,39 +5032,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.595</v>
+        <v>1.18</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.0165</v>
+        <v>-0.0248</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2371200</v>
+        <v>2545200</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.43</v>
+        <v>1.14</v>
       </c>
       <c r="H102" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I102" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.53</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.554</v>
+        <v>1.279</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.498</v>
+        <v>1.309</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5077,39 +5077,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.295</v>
+        <v>3.61</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0167</v>
+        <v>-0.0137</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2322400</v>
+        <v>2538500</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H103" t="n">
-        <v>52.19</v>
-      </c>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.292</v>
+        <v>3.597</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.281</v>
+        <v>2.783</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5131,19 +5131,19 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E104" s="9" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.77</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>2294900</v>
+        <v>2439700</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="H104" t="n">
-        <v>64.31999999999999</v>
+        <v>62.45</v>
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.695</v>
+        <v>0.694</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5167,28 +5167,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>3.54</v>
+        <v>0.435</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>-0.0328</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>2279000</v>
+        <v>2419800</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.21</v>
+        <v>0.67</v>
       </c>
       <c r="H105" t="n">
-        <v>52.25</v>
+        <v>44.67</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3.591</v>
+        <v>0.456</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2.782</v>
+        <v>0.422</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5212,39 +5212,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>0.445</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.0326</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>2241200</v>
+        <v>2401700</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="H106" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.65</v>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.927</v>
+        <v>0.451</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.956</v>
+        <v>0.428</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5257,39 +5257,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>-0.0189</v>
+        <v>1.91</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2231100</v>
+        <v>2242100</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1.13</v>
+        <v>0.35</v>
       </c>
       <c r="H107" t="n">
-        <v>62.06</v>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.23</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.494</v>
+        <v>1.927</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.481</v>
+        <v>1.956</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5302,39 +5302,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.435</v>
+        <v>0.52</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0189</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>2199300</v>
+        <v>2241300</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.61</v>
+        <v>1.13</v>
       </c>
       <c r="H108" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.06</v>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.456</v>
+        <v>0.494</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.422</v>
+        <v>0.481</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5356,19 +5356,19 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>2138300</v>
+        <v>2142700</v>
       </c>
       <c r="G109" s="5" t="n">
         <v>0.34</v>
       </c>
       <c r="H109" t="n">
-        <v>35.77</v>
+        <v>35.18</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>3.456</v>
+        <v>3.455</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>3.646</v>
+        <v>3.645</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
         <v>-0.004699999999999999</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>2043200</v>
+        <v>2070700</v>
       </c>
       <c r="G110" s="5" t="n">
         <v>0.24</v>
@@ -5482,40 +5482,36 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1969400</v>
+        <v>1982800</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1.17</v>
+        <v>0.2</v>
       </c>
       <c r="H112" t="n">
-        <v>58.47</v>
+        <v>66.19</v>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J112" s="2" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>0.19</v>
-      </c>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
     </row>
@@ -5527,39 +5523,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>-0.0208</v>
+        <v>0.22</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1949400</v>
+        <v>1977000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.63</v>
+        <v>1.18</v>
       </c>
       <c r="H113" t="n">
-        <v>46.24</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.47</v>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.241</v>
+        <v>0.212</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.249</v>
+        <v>0.19</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5572,36 +5568,40 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.34</v>
+        <v>0.235</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.0286</v>
+        <v>-0.0208</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1942800</v>
+        <v>1949700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="H114" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="n"/>
+        <v>46.24</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.249</v>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
     </row>
@@ -5613,39 +5613,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.41</v>
+        <v>1.02</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>0.0123</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1910400</v>
+        <v>1922500</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>1.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>39.23</v>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.95</v>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.421</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.44</v>
+        <v>0.494</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5658,28 +5658,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>-0.0109</v>
+        <v>0.41</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1902000</v>
+        <v>1910400</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.36</v>
+        <v>1.24</v>
       </c>
       <c r="H116" t="n">
-        <v>54.32</v>
+        <v>39.23</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.908</v>
+        <v>0.421</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.865</v>
+        <v>0.44</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5703,39 +5703,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E117" s="9" t="n">
-        <v>0.0052</v>
+        <v>0.91</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1866400</v>
+        <v>1902500</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="H117" t="n">
-        <v>34.31</v>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.32</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.993</v>
+        <v>0.908</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.065</v>
+        <v>0.865</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
         <v>-0.0155</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1861600</v>
+        <v>1887700</v>
       </c>
       <c r="G118" s="5" t="n">
         <v>0.48</v>
@@ -5793,28 +5793,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E119" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.955</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1853900</v>
+        <v>1880700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H119" t="n">
-        <v>86.95</v>
+        <v>32.16</v>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.494</v>
+        <v>1.065</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5838,39 +5838,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>1.72</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.0282</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1836300</v>
+        <v>1838900</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>1.79</v>
+        <v>0.3</v>
       </c>
       <c r="H120" t="n">
-        <v>51.47</v>
-      </c>
-      <c r="I120" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.67</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.203</v>
+        <v>1.814</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.211</v>
+        <v>1.921</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5883,28 +5883,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>-0.011</v>
+        <v>0.205</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1773300</v>
+        <v>1836300</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.26</v>
+        <v>1.79</v>
       </c>
       <c r="H121" t="n">
-        <v>58.92</v>
+        <v>51.47</v>
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.428</v>
+        <v>0.203</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.414</v>
+        <v>0.211</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5928,39 +5928,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="E122" s="9" t="n">
-        <v>0.0025</v>
+        <v>0.82</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1766200</v>
+        <v>1823700</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.42</v>
+        <v>0.28</v>
       </c>
       <c r="H122" t="n">
-        <v>72.77</v>
-      </c>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>7.314</v>
+        <v>0.757</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>6.791</v>
+        <v>0.668</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5973,39 +5973,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>-0.0145</v>
+        <v>-0.011</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1730500</v>
+        <v>1810700</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.31</v>
+        <v>0.26</v>
       </c>
       <c r="H123" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.92</v>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.348</v>
+        <v>0.428</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.381</v>
+        <v>0.414</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6018,39 +6018,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>-0.024</v>
+        <v>7.98</v>
+      </c>
+      <c r="E124" s="9" t="n">
+        <v>0.0025</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1730400</v>
+        <v>1793000</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="H124" t="n">
-        <v>67.59</v>
-      </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.77</v>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.757</v>
+        <v>7.314</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.668</v>
+        <v>6.791</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6063,28 +6063,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1.72</v>
+        <v>0.34</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-0.0282</v>
+        <v>-0.0145</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1689300</v>
+        <v>1730500</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.28</v>
+        <v>1.31</v>
       </c>
       <c r="H125" t="n">
-        <v>35.67</v>
+        <v>37.96</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.814</v>
+        <v>0.348</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1.921</v>
+        <v>0.381</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6108,39 +6108,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>3.13</v>
+        <v>2.02</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.031</v>
+        <v>-0.0335</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1629700</v>
+        <v>1717400</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="H126" t="n">
-        <v>42.01</v>
-      </c>
-      <c r="I126" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.07</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>3.19</v>
+        <v>2.055</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>3.381</v>
+        <v>2.083</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6153,28 +6153,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>0.0089</v>
+        <v>0.0025</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1627600</v>
+        <v>1655800</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>51.15</v>
+        <v>51.33</v>
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>7.892</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>7.855</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6198,28 +6198,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E128" s="9" t="n">
-        <v>0.0038</v>
+        <v>3.14</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.0279</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1624200</v>
+        <v>1636400</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.54</v>
+        <v>0.36</v>
       </c>
       <c r="H128" t="n">
-        <v>51.9</v>
+        <v>42.66</v>
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>7.893</v>
+        <v>3.191</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>7.856</v>
+        <v>3.381</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6252,19 +6252,19 @@
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.59</v>
+        <v>0.585</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>-0.0167</v>
+        <v>-0.025</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1620200</v>
+        <v>1635300</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H129" t="n">
-        <v>37.34</v>
+        <v>35.84</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6297,19 +6297,19 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>5.88</v>
+        <v>5.87</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.0034</v>
+        <v>-0.0051</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1615700</v>
+        <v>1635100</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H130" t="n">
-        <v>62.42</v>
+        <v>62.08</v>
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>5.516</v>
+        <v>5.515</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>5.374</v>
+        <v>5.373</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6342,19 +6342,19 @@
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0112</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1610100</v>
+        <v>1631100</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H131" t="n">
-        <v>51.65</v>
+        <v>50.14</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.756</v>
+        <v>1.755</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>1.778</v>
@@ -6378,28 +6378,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>7.95</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>0.0474</v>
+        <v>0.0089</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1594000</v>
+        <v>1627600</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H132" t="n">
-        <v>55.98</v>
+        <v>51.15</v>
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>7.753</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>7.899</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6432,19 +6432,19 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E133" s="9" t="n">
-        <v>0.0105</v>
+        <v>0.475</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1551600</v>
+        <v>1623500</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="H133" t="n">
-        <v>58.28</v>
+        <v>56.57</v>
       </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
@@ -6452,10 +6452,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6468,39 +6468,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>-0.008399999999999999</v>
+        <v>7.97</v>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>0.0501</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1535000</v>
+        <v>1612100</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>2.82</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>40.76</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.55</v>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.195</v>
+        <v>7.755</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>1.212</v>
+        <v>7.899</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6513,39 +6513,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.6</v>
+        <v>1.07</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.0323</v>
+        <v>-0.036</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1514200</v>
+        <v>1571300</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="H135" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="I135" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.17</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.614</v>
+        <v>1.058</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.608</v>
+        <v>0.901</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6558,39 +6558,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>-0.0287</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1506100</v>
+        <v>1535000</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.47</v>
+        <v>2.82</v>
       </c>
       <c r="H136" t="n">
-        <v>44.47</v>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.76</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2.056</v>
+        <v>1.195</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.083</v>
+        <v>1.212</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6603,28 +6603,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1478800</v>
+        <v>1521100</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="H137" t="n">
-        <v>37.81</v>
+        <v>58.06</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.329</v>
+        <v>0.252</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.33</v>
+        <v>0.221</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6648,39 +6648,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.83</v>
+        <v>0.6</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.0323</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1463500</v>
+        <v>1515500</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="H138" t="n">
-        <v>44.42</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.87</v>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2.954</v>
+        <v>0.614</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>2.834</v>
+        <v>0.608</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6693,28 +6693,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0</v>
+        <v>0.31</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1435000</v>
+        <v>1486300</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1.39</v>
+        <v>0.75</v>
       </c>
       <c r="H139" t="n">
-        <v>41.54</v>
+        <v>37.81</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.273</v>
+        <v>0.329</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.276</v>
+        <v>0.33</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6738,28 +6738,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.26</v>
+        <v>2.84</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0173</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1422300</v>
+        <v>1484100</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H140" t="n">
-        <v>58.06</v>
+        <v>44.87</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.252</v>
+        <v>2.955</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.221</v>
+        <v>2.835</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6783,39 +6783,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>2.85</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1402900</v>
+        <v>1455700</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H141" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.94</v>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.338</v>
+        <v>2.785</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.344</v>
+        <v>2.612</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6828,28 +6828,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>-0.018</v>
+        <v>0.27</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1392900</v>
+        <v>1435000</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.17</v>
+        <v>1.39</v>
       </c>
       <c r="H142" t="n">
-        <v>32.64</v>
+        <v>41.54</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>7.382</v>
+        <v>0.273</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>7.709</v>
+        <v>0.276</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6873,28 +6873,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.905</v>
+        <v>0.355</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>-0.0163</v>
+        <v>-0.0274</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1392800</v>
+        <v>1427700</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.46</v>
+        <v>0.91</v>
       </c>
       <c r="H143" t="n">
-        <v>44.8</v>
+        <v>42.28</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6902,10 +6902,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.911</v>
+        <v>0.363</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.963</v>
+        <v>0.387</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6918,39 +6918,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.85</v>
+        <v>7.12</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>-0.0035</v>
+        <v>-0.0152</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1368900</v>
+        <v>1417800</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H144" t="n">
-        <v>56.94</v>
-      </c>
-      <c r="I144" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.24</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>2.785</v>
+        <v>7.384</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>2.612</v>
+        <v>7.709</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6963,39 +6963,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>-0.018</v>
+        <v>0.325</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1367900</v>
+        <v>1407100</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="H145" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="I145" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.39</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.06</v>
+        <v>0.338</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.902</v>
+        <v>0.344</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -7008,39 +7008,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E146" s="9" t="n">
-        <v>0.0313</v>
+        <v>0.9</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1302100</v>
+        <v>1399900</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>2.76</v>
+        <v>0.46</v>
       </c>
       <c r="H146" t="n">
-        <v>64.79000000000001</v>
-      </c>
-      <c r="I146" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.3</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.313</v>
+        <v>0.911</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.316</v>
+        <v>0.963</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7053,28 +7053,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>-0.0058</v>
+        <v>0.39</v>
+      </c>
+      <c r="E147" s="9" t="n">
+        <v>0.0541</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1274800</v>
+        <v>1392600</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="H147" t="n">
-        <v>56.02</v>
+        <v>55.53</v>
       </c>
       <c r="I147" s="8" t="inlineStr">
         <is>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.669</v>
+        <v>0.368</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1.678</v>
+        <v>0.375</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7098,39 +7098,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.36</v>
+        <v>1.7</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>-0.0137</v>
+        <v>-0.0173</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1227700</v>
+        <v>1380700</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H148" t="n">
-        <v>44.79</v>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.72</v>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.364</v>
+        <v>1.667</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.387</v>
+        <v>1.677</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7143,28 +7143,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.255</v>
+        <v>5.95</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.0133</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1222500</v>
+        <v>1318900</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="H149" t="n">
-        <v>61.4</v>
+        <v>34.76</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.235</v>
+        <v>6.144</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.209</v>
+        <v>6.388</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7188,39 +7188,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.73</v>
+        <v>0.24</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>-0.0135</v>
+        <v>-0.0204</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1222300</v>
+        <v>1303300</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H150" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.93</v>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.758</v>
+        <v>0.237</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.748</v>
+        <v>0.243</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7233,28 +7233,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>-0.0492</v>
+        <v>0.33</v>
+      </c>
+      <c r="E151" s="9" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1213500</v>
+        <v>1302100</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1.26</v>
+        <v>2.76</v>
       </c>
       <c r="H151" t="n">
-        <v>67.25</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.268</v>
+        <v>0.313</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.265</v>
+        <v>0.316</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7293,10 +7293,10 @@
         <v>-0.0247</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1200400</v>
+        <v>1251400</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H152" t="n">
         <v>53.25</v>
@@ -7323,39 +7323,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>0.46</v>
+        <v>0.735</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>-0.0213</v>
+        <v>-0.0068</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1195100</v>
+        <v>1224300</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H153" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="I153" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.09</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.447</v>
+        <v>0.758</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0.451</v>
+        <v>0.748</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7368,39 +7368,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E154" s="9" t="n">
-        <v>0.0111</v>
+        <v>0.255</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1188400</v>
+        <v>1223000</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H154" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I154" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.4</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>2.638</v>
+        <v>0.235</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>2.588</v>
+        <v>0.209</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7413,39 +7413,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>IWCITY</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>-0.0492</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1162700</v>
+        <v>1213500</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="H155" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.25</v>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.208</v>
+        <v>0.268</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.221</v>
+        <v>0.265</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7458,39 +7458,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>-0.0292</v>
+        <v>-0.011</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1137700</v>
+        <v>1203600</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="H156" t="n">
-        <v>55.05</v>
-      </c>
-      <c r="I156" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.36</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.299</v>
+        <v>1.874</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1.202</v>
+        <v>2.009</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7503,28 +7503,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>-0.0204</v>
+        <v>-0.0213</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>1123500</v>
+        <v>1195100</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H157" t="n">
-        <v>59.28</v>
+        <v>55.29</v>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.232</v>
+        <v>0.447</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0.204</v>
+        <v>0.451</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7548,39 +7548,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>-0.0136</v>
+        <v>2.73</v>
+      </c>
+      <c r="E158" s="9" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>1106800</v>
+        <v>1188500</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="H158" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.38</v>
+      </c>
+      <c r="I158" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2.97</v>
+        <v>2.638</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>3.033</v>
+        <v>2.588</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7593,39 +7593,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>-0.0484</v>
+        <v>0.2</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1106800</v>
+        <v>1165700</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="H159" t="n">
-        <v>57.34</v>
-      </c>
-      <c r="I159" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.61</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.58</v>
+        <v>0.208</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0.543</v>
+        <v>0.221</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7638,28 +7638,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>-0.011</v>
+        <v>5.48</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>1100100</v>
+        <v>1163100</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="H160" t="n">
-        <v>34.36</v>
+        <v>34.21</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>1.874</v>
+        <v>5.691</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>2.009</v>
+        <v>5.859</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7683,28 +7683,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.21</v>
+        <v>0.54</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>-0.0472</v>
+        <v>-0.0182</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>1096600</v>
+        <v>1151100</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H161" t="n">
-        <v>63.25</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1.097</v>
+        <v>0.483</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.841</v>
+        <v>0.454</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7728,39 +7728,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>1.33</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>-0.0292</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>1095100</v>
+        <v>1145700</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="H162" t="n">
-        <v>25.54</v>
-      </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.05</v>
+      </c>
+      <c r="I162" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.952</v>
+        <v>1.299</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0.99</v>
+        <v>1.202</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7773,39 +7773,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>-0.0403</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>1090600</v>
+        <v>1144900</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="H163" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.38</v>
+      </c>
+      <c r="I163" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.116</v>
+        <v>0.58</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1.091</v>
+        <v>0.543</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7818,39 +7818,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>-0.0472</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>1089100</v>
+        <v>1141800</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="H164" t="n">
-        <v>34.21</v>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.25</v>
+      </c>
+      <c r="I164" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>5.691</v>
+        <v>1.097</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>5.859</v>
+        <v>0.841</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7863,28 +7863,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.0136</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>1087800</v>
+        <v>1133000</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="H165" t="n">
-        <v>54.02</v>
+        <v>43.56</v>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>2.463</v>
+        <v>2.97</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>2.352</v>
+        <v>3.033</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7908,28 +7908,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E166" s="9" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.24</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>1080000</v>
+        <v>1129200</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H166" t="n">
-        <v>56.61</v>
+        <v>59.28</v>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>2.094</v>
+        <v>0.232</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>2.041</v>
+        <v>0.204</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7953,39 +7953,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0.245</v>
+        <v>0.9</v>
       </c>
       <c r="E167" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>1078300</v>
+        <v>1118900</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="H167" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="I167" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.54</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.237</v>
+        <v>0.952</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0.243</v>
+        <v>0.99</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7998,39 +7998,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>0</v>
+        <v>2.48</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>1050600</v>
+        <v>1108400</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="H168" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="I168" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.51</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.641</v>
+        <v>2.464</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0.604</v>
+        <v>2.353</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8043,28 +8043,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E169" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.92</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>1047800</v>
+        <v>1100000</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="H169" t="n">
-        <v>37.75</v>
+        <v>31.56</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.581</v>
+        <v>0.962</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.621</v>
+        <v>1.019</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8088,28 +8088,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>-0.0062</v>
+        <v>2.13</v>
+      </c>
+      <c r="E170" s="9" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>1040800</v>
+        <v>1097400</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H170" t="n">
-        <v>79.31999999999999</v>
+        <v>55.69</v>
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>2.093</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>0.627</v>
+        <v>2.041</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8133,39 +8133,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>-0.0273</v>
+        <v>1.11</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>1015700</v>
+        <v>1090600</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.25</v>
+        <v>0.68</v>
       </c>
       <c r="H171" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I171" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.28</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.483</v>
+        <v>1.116</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>0.454</v>
+        <v>1.091</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8178,39 +8178,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>6</v>
+        <v>0.795</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>-0.005</v>
+        <v>-0.0124</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>1014900</v>
+        <v>1060900</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="H172" t="n">
-        <v>36.95</v>
-      </c>
-      <c r="I172" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.65000000000001</v>
+      </c>
+      <c r="I172" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>6.148</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>6.389</v>
+        <v>0.626</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8223,39 +8223,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>-0.0216</v>
+        <v>0.67</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>993600</v>
+        <v>1051300</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H173" t="n">
-        <v>28.82</v>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.99</v>
+      </c>
+      <c r="I173" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.961</v>
+        <v>0.641</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1.018</v>
+        <v>0.604</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8268,28 +8268,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1.38</v>
+        <v>0.555</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>0.0073</v>
+        <v>0.0183</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>966500</v>
+        <v>1047800</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H174" t="n">
-        <v>72.79000000000001</v>
+        <v>37.75</v>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>1.25</v>
+        <v>0.581</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>1.02</v>
+        <v>0.621</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8313,28 +8313,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>0.655</v>
+        <v>1.4</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>0.0077</v>
+        <v>0.0219</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>879500</v>
+        <v>976800</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="H175" t="n">
-        <v>61.06</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.625</v>
+        <v>1.252</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>0.533</v>
+        <v>1.02</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8358,39 +8358,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0.63</v>
+        <v>3.03</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0066</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>868700</v>
+        <v>946400</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H176" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="I176" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.36</v>
+      </c>
+      <c r="I176" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.638</v>
+        <v>2.725</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>0.612</v>
+        <v>2.073</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8403,28 +8403,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>2.17</v>
+        <v>0.655</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>0.0046</v>
+        <v>0.0077</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>849300</v>
+        <v>941400</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="H177" t="n">
-        <v>49.11</v>
+        <v>61.06</v>
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>2.185</v>
+        <v>0.625</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>2.132</v>
+        <v>0.533</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8448,39 +8448,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>838400</v>
+        <v>871200</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="H178" t="n">
-        <v>50.56</v>
-      </c>
-      <c r="I178" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46</v>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>1.25</v>
+        <v>0.637</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>1.284</v>
+        <v>0.612</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8493,28 +8493,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>-0.0247</v>
+        <v>2.18</v>
+      </c>
+      <c r="E179" s="9" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>821600</v>
+        <v>864200</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.73</v>
+        <v>0.17</v>
       </c>
       <c r="H179" t="n">
-        <v>33.84</v>
+        <v>49.97</v>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>1.68</v>
+        <v>2.186</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>1.811</v>
+        <v>2.132</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8538,28 +8538,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>-0.0033</v>
+        <v>1.26</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>817700</v>
+        <v>857400</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="H180" t="n">
-        <v>68.89</v>
+        <v>50.56</v>
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>2.726</v>
+        <v>1.25</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>2.073</v>
+        <v>1.284</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8583,28 +8583,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TROP</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E181" s="9" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.58</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>-0.0247</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>801800</v>
+        <v>822400</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="H181" t="n">
-        <v>49.35</v>
+        <v>33.84</v>
       </c>
       <c r="I181" s="6" t="inlineStr">
         <is>
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>1.181</v>
+        <v>1.68</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>1.191</v>
+        <v>1.811</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8628,39 +8628,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>11.24</v>
+        <v>1.18</v>
       </c>
       <c r="E182" s="9" t="n">
-        <v>0.0218</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>780400</v>
+        <v>801800</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.23</v>
+        <v>0.77</v>
       </c>
       <c r="H182" t="n">
-        <v>76.12</v>
-      </c>
-      <c r="I182" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.35</v>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>10.33</v>
+        <v>1.181</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>9.566000000000001</v>
+        <v>1.191</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8673,39 +8673,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>RCECAP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>0.0152</v>
+        <v>0.0083</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>777500</v>
+        <v>795500</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>1.37</v>
+        <v>0.19</v>
       </c>
       <c r="H183" t="n">
-        <v>55.68</v>
-      </c>
-      <c r="I183" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.13</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.982</v>
+        <v>1.16</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>1.014</v>
+        <v>1.074</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8718,39 +8718,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>-0.0145</v>
+        <v>11.26</v>
+      </c>
+      <c r="E184" s="9" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>775200</v>
+        <v>785800</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.73</v>
+        <v>0.23</v>
       </c>
       <c r="H184" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.31999999999999</v>
+      </c>
+      <c r="I184" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>2.197</v>
+        <v>10.332</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>2.31</v>
+        <v>9.567</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8763,39 +8763,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E185" s="9" t="n">
-        <v>0.0291</v>
+        <v>2.03</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>-0.0193</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>774400</v>
+        <v>781400</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="H185" t="n">
-        <v>53.72</v>
-      </c>
-      <c r="I185" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.33</v>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.861</v>
+        <v>2.196</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>0.922</v>
+        <v>2.31</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
@@ -8808,39 +8808,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>RCECAP</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>-0.0083</v>
+        <v>1</v>
+      </c>
+      <c r="E186" s="9" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>762300</v>
+        <v>777500</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.18</v>
+        <v>1.37</v>
       </c>
       <c r="H186" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="I186" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.68</v>
+      </c>
+      <c r="I186" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>1.158</v>
+        <v>0.982</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>1.073</v>
+        <v>1.014</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
@@ -8853,28 +8853,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E187" s="3" t="n">
-        <v>-0.0327</v>
+        <v>0.88</v>
+      </c>
+      <c r="E187" s="9" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>750000</v>
+        <v>774500</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="H187" t="n">
-        <v>51.26</v>
+        <v>52.53</v>
       </c>
       <c r="I187" s="8" t="inlineStr">
         <is>
@@ -8882,10 +8882,10 @@
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.736</v>
+        <v>0.86</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>0.724</v>
+        <v>0.921</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
@@ -8907,19 +8907,19 @@
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>-0.0117</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>747600</v>
+        <v>771700</v>
       </c>
       <c r="G188" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="H188" t="n">
-        <v>43.44</v>
+        <v>43.77</v>
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>4.36</v>
+        <v>4.361</v>
       </c>
       <c r="K188" s="2" t="n">
         <v>4.456</v>
@@ -8943,39 +8943,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>0.875</v>
+        <v>0.74</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>-0.0223</v>
+        <v>-0.0327</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>728700</v>
+        <v>750700</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="H189" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="I189" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.26</v>
+      </c>
+      <c r="I189" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>1.019</v>
+        <v>0.736</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>1.113</v>
+        <v>0.724</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="7" t="inlineStr"/>
@@ -8988,39 +8988,39 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E190" s="9" t="n">
-        <v>0.004</v>
+        <v>0.875</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>690200</v>
+        <v>734700</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="H190" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="I190" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>17.67</v>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>2.574</v>
+        <v>1.019</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>2.723</v>
+        <v>1.113</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
@@ -9033,39 +9033,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>-0.012</v>
+        <v>2.51</v>
+      </c>
+      <c r="E191" s="9" t="n">
+        <v>0.004</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>682700</v>
+        <v>720700</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>0.47</v>
+        <v>0.22</v>
       </c>
       <c r="H191" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.83</v>
+      </c>
+      <c r="I191" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J191" s="2" t="n">
-        <v>1.774</v>
+        <v>2.574</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>1.913</v>
+        <v>2.723</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="7" t="inlineStr"/>
@@ -9078,39 +9078,39 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>0.925</v>
+        <v>1.07</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>-0.0107</v>
+        <v>-0.0183</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>664200</v>
+        <v>705000</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="H192" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="I192" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.26</v>
+      </c>
+      <c r="I192" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.923</v>
+        <v>1.101</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>0.854</v>
+        <v>1.145</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="7" t="inlineStr"/>
@@ -9123,28 +9123,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>-0.0072</v>
+        <v>-0.012</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>657700</v>
+        <v>685900</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="H193" t="n">
-        <v>31.93</v>
+        <v>29.39</v>
       </c>
       <c r="I193" s="6" t="inlineStr">
         <is>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>1.449</v>
+        <v>1.774</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>1.491</v>
+        <v>1.913</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="7" t="inlineStr"/>
@@ -9168,39 +9168,39 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>1.56</v>
+        <v>0.925</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.0107</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>655000</v>
+        <v>680800</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="H194" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I194" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.85</v>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>1.565</v>
+        <v>0.923</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>1.616</v>
+        <v>0.854</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="7" t="inlineStr"/>
@@ -9213,28 +9213,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>1.07</v>
+        <v>1.56</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>-0.0183</v>
+        <v>-0.0189</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>625100</v>
+        <v>665400</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>0.53</v>
+        <v>0.16</v>
       </c>
       <c r="H195" t="n">
-        <v>40.26</v>
+        <v>47.4</v>
       </c>
       <c r="I195" s="8" t="inlineStr">
         <is>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>1.101</v>
+        <v>1.565</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>1.145</v>
+        <v>1.616</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="7" t="inlineStr"/>
@@ -9258,39 +9258,39 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>3.2</v>
+        <v>1.39</v>
       </c>
       <c r="E196" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>593200</v>
+        <v>661000</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H196" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I196" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.33</v>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>3.02</v>
+        <v>1.45</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>2.817</v>
+        <v>1.491</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="7" t="inlineStr"/>
@@ -9303,28 +9303,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>0.82</v>
+        <v>3.19</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>-0.0296</v>
+        <v>-0.0031</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>577400</v>
+        <v>617300</v>
       </c>
       <c r="G197" s="5" t="n">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="H197" t="n">
-        <v>48.27</v>
+        <v>61.32</v>
       </c>
       <c r="I197" s="8" t="inlineStr">
         <is>
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.824</v>
+        <v>3.019</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>0.838</v>
+        <v>2.816</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="7" t="inlineStr"/>
@@ -9363,10 +9363,10 @@
         <v>-0.0438</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>574500</v>
+        <v>604900</v>
       </c>
       <c r="G198" s="5" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H198" t="n">
         <v>39.98</v>
@@ -9393,28 +9393,28 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>-0.0217</v>
+        <v>0.54</v>
+      </c>
+      <c r="E199" s="9" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>556800</v>
+        <v>579100</v>
       </c>
       <c r="G199" s="5" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H199" t="n">
-        <v>39.64</v>
+        <v>39.51</v>
       </c>
       <c r="I199" s="6" t="inlineStr">
         <is>
@@ -9422,10 +9422,10 @@
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0.921</v>
+        <v>0.551</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="7" t="inlineStr"/>
@@ -9438,28 +9438,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>TEOSENG</t>
         </is>
       </c>
       <c r="D200" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E200" s="10" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>-0.0296</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>553100</v>
+        <v>578600</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>0.32</v>
+        <v>1.12</v>
       </c>
       <c r="H200" t="n">
-        <v>46.98</v>
+        <v>48.27</v>
       </c>
       <c r="I200" s="8" t="inlineStr">
         <is>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>1.061</v>
+        <v>0.824</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>1.19</v>
+        <v>0.838</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" s="7" t="inlineStr"/>
@@ -9483,28 +9483,28 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E201" s="9" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>547600</v>
+        <v>577500</v>
       </c>
       <c r="G201" s="5" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="H201" t="n">
-        <v>39.51</v>
+        <v>41.27</v>
       </c>
       <c r="I201" s="6" t="inlineStr">
         <is>
@@ -9512,10 +9512,10 @@
         </is>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.551</v>
+        <v>0.921</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>0.58</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" s="7" t="inlineStr"/>
@@ -9528,39 +9528,39 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>0.625</v>
+        <v>1.06</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>541000</v>
+        <v>554400</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="H202" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="I202" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.02</v>
+      </c>
+      <c r="I202" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.632</v>
+        <v>1.06</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>0.63</v>
+        <v>1.19</v>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" s="7" t="inlineStr"/>
@@ -9573,39 +9573,39 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0351</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>LSH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>1.68</v>
+        <v>0.625</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>-0.0289</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>526500</v>
+        <v>541000</v>
       </c>
       <c r="G203" s="5" t="n">
-        <v>0.73</v>
+        <v>0.44</v>
       </c>
       <c r="H203" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I203" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.25</v>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>1.657</v>
+        <v>0.632</v>
       </c>
       <c r="K203" s="2" t="n">
-        <v>1.615</v>
+        <v>0.63</v>
       </c>
       <c r="L203" t="inlineStr"/>
       <c r="M203" s="7" t="inlineStr"/>
@@ -9618,28 +9618,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0185</t>
+          <t>0351</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>HSSEB</t>
+          <t>LSH</t>
         </is>
       </c>
       <c r="D204" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E204" s="9" t="n">
-        <v>0.02</v>
+        <v>1.68</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>-0.0289</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>520900</v>
+        <v>537500</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>1.96</v>
+        <v>0.74</v>
       </c>
       <c r="H204" t="n">
-        <v>64.33</v>
+        <v>55.02</v>
       </c>
       <c r="I204" s="8" t="inlineStr">
         <is>
@@ -9647,10 +9647,10 @@
         </is>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.473</v>
+        <v>1.657</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>0.498</v>
+        <v>1.615</v>
       </c>
       <c r="L204" t="inlineStr"/>
       <c r="M204" s="7" t="inlineStr"/>
@@ -9663,28 +9663,28 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>1.38</v>
+        <v>6.76</v>
       </c>
       <c r="E205" s="9" t="n">
-        <v>0.0073</v>
+        <v>0.0075</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>504600</v>
+        <v>536300</v>
       </c>
       <c r="G205" s="5" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H205" t="n">
-        <v>57.8</v>
+        <v>49.65</v>
       </c>
       <c r="I205" s="6" t="inlineStr">
         <is>
@@ -9692,16 +9692,196 @@
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>1.37</v>
+        <v>6.765</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>1.338</v>
+        <v>6.846</v>
       </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" s="7" t="inlineStr"/>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>0185</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>HSSEB</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E206" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F206" s="4" t="n">
+        <v>531800</v>
+      </c>
+      <c r="G206" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="I206" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="K206" s="2" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" s="7" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>-0.0356</v>
+      </c>
+      <c r="F207" s="4" t="n">
+        <v>528500</v>
+      </c>
+      <c r="G207" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H207" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K207" s="2" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" s="7" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>5819</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>HLBANK</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E208" s="9" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="F208" s="4" t="n">
+        <v>514200</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H208" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="n">
+        <v>21.979</v>
+      </c>
+      <c r="K208" s="2" t="n">
+        <v>22.105</v>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" s="7" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E209" s="9" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F209" s="4" t="n">
+        <v>505400</v>
+      </c>
+      <c r="G209" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H209" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K209" s="2" t="n">
+        <v>1.338</v>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M205"/>
+  <autoFilter ref="A1:M209"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>